--- a/Versão5/AVAC/Ontologia_AVAC.xlsx
+++ b/Versão5/AVAC/Ontologia_AVAC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AVAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15BF242B-429C-4CAB-BEE1-5A45E428EA54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FE1C2EC-C257-4786-9129-DBB952060335}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3177" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3228" uniqueCount="503">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1537,6 +1537,51 @@
   </si>
   <si>
     <t>Elementos.de.Acessórios</t>
+  </si>
+  <si>
+    <t>Os aquecedores de ambiente utilizam uma combinação de radiação e/ou convecção natural.</t>
+  </si>
+  <si>
+    <t>Los calefactores utilizan una combinación de radiación natural y/o convección.</t>
+  </si>
+  <si>
+    <t>Arquitetura</t>
+  </si>
+  <si>
+    <t>Unidade de distribuição de calor que opera com ar circulado por gravidade.</t>
+  </si>
+  <si>
+    <t>Unidad de distribución de calor que funciona con aire circulado por gravedad.</t>
+  </si>
+  <si>
+    <t>Unidade de distribuição de calor que opera com radiação térmica.</t>
+  </si>
+  <si>
+    <t>Unidad de distribución de calor que funciona con radiación térmica.</t>
+  </si>
+  <si>
+    <t>Avac.Equipamentos.Unitarios</t>
+  </si>
+  <si>
+    <t>Avac.Aquecedor.de.Ambiente</t>
+  </si>
+  <si>
+    <t>Avac.Aquecedor.Convector</t>
+  </si>
+  <si>
+    <t>Avac.Aquecedor.Radiação</t>
+  </si>
+  <si>
+    <t>[ OST_SpecialityEquipment ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpaceHeater ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpaceHeaterCONVECTOR ]</t>
+  </si>
+  <si>
+    <t>[ IfcSpaceHeaterRADIATOR ]</t>
   </si>
 </sst>
 </file>
@@ -2084,7 +2129,56 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="143">
+  <dxfs count="183">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2112,6 +2206,52 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color rgb="FFFFFFFF"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2511,24 +2651,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -2539,6 +2668,62 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2580,14 +2765,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -2595,14 +2772,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color rgb="FFFFFFFF"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2626,11 +2795,73 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3000,11 +3231,151 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <b val="0"/>
         <i/>
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3061,6 +3432,74 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -4113,7 +4552,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46139.728779398145</v>
+        <v>46139.740276273151</v>
       </c>
       <c r="C18" s="56" t="s">
         <v>208</v>
@@ -4218,7 +4657,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA86"/>
+  <dimension ref="A1:AA89"/>
   <sheetFormatPr defaultColWidth="7.84375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.53515625" customWidth="1"/>
@@ -4230,11 +4669,11 @@
     <col min="7" max="7" width="4.69140625" style="41" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.765625" style="41" bestFit="1" customWidth="1"/>
     <col min="9" max="11" width="4.69140625" style="41" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.61328125" customWidth="1"/>
-    <col min="13" max="13" width="10.23046875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.23046875" customWidth="1"/>
-    <col min="15" max="15" width="14.3828125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="64.61328125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.69140625" customWidth="1"/>
+    <col min="13" max="13" width="13.69140625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.69140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.69140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="66" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="53.69140625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7.921875" customWidth="1"/>
@@ -4419,7 +4858,7 @@
         <v>9</v>
       </c>
       <c r="AA2" s="32" t="str">
-        <f t="shared" ref="AA2:AA65" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
+        <f t="shared" ref="AA2:AA68" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
@@ -4498,7 +4937,7 @@
         <v>232</v>
       </c>
       <c r="W3" s="68" t="str">
-        <f t="shared" ref="W3:W66" si="4">CONCATENATE("Key-AVA-",A3)</f>
+        <f t="shared" ref="W3:W69" si="4">CONCATENATE("Key-AVA-",A3)</f>
         <v>Key-AVA-3</v>
       </c>
       <c r="X3" s="32" t="s">
@@ -5114,7 +5553,7 @@
         <v>Sistema Climatizador</v>
       </c>
       <c r="O10" s="32" t="str">
-        <f t="shared" ref="O10:O51" si="7">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("",F10),CONCATENATE("",F10))</f>
+        <f t="shared" ref="O10:O54" si="7">IF(ISNUMBER(FIND("Ifc",F10)),CONCATENATE("",F10),CONCATENATE("",F10))</f>
         <v>Ar.Condicionado</v>
       </c>
       <c r="P10" s="32" t="s">
@@ -5846,7 +6285,7 @@
         <v>Sistemas.de.Climatização</v>
       </c>
       <c r="N18" s="37" t="str">
-        <f t="shared" ref="N18:O60" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N18:O63" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E18),"."," ")," De "," de "))</f>
         <v>Sistema Climatizador</v>
       </c>
       <c r="O18" s="32" t="str">
@@ -7586,7 +8025,7 @@
         <v>9</v>
       </c>
       <c r="L37" s="37" t="str">
-        <f t="shared" ref="L37:M86" si="11">CONCATENATE("", C37)</f>
+        <f t="shared" ref="L37:M89" si="11">CONCATENATE("", C37)</f>
         <v>Climatização</v>
       </c>
       <c r="M37" s="37" t="str">
@@ -8657,7 +9096,7 @@
     </row>
     <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="34">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>43</v>
@@ -8665,22 +9104,22 @@
       <c r="C49" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D49" s="35" t="s">
-        <v>464</v>
-      </c>
-      <c r="E49" s="35" t="s">
-        <v>422</v>
+      <c r="D49" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>383</v>
+        <v>496</v>
       </c>
       <c r="G49" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H49" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I49" s="42" t="s">
+      <c r="H49" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I49" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J49" s="42" t="s">
@@ -8695,61 +9134,61 @@
       </c>
       <c r="M49" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.AntiVibração</v>
+        <v>Elementos.de.Climatização</v>
       </c>
       <c r="N49" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Dampers</v>
-      </c>
-      <c r="O49" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Avac.Amortecedor</v>
+        <v>Avac Equipamentos Unitarios</v>
+      </c>
+      <c r="O49" s="37" t="str">
+        <f t="shared" ref="O49:O51" si="13">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F49),"."," ")," De "," de "))</f>
+        <v>Avac Aquecedor de Ambiente</v>
       </c>
       <c r="P49" s="32" t="s">
-        <v>81</v>
+        <v>488</v>
       </c>
       <c r="Q49" s="32" t="s">
-        <v>129</v>
+        <v>489</v>
       </c>
       <c r="R49" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S49" s="39" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="S49:S51" si="14">SUBSTITUTE(C49, ".", " ")</f>
         <v>Climatização</v>
       </c>
       <c r="T49" s="39" t="str">
-        <f t="shared" si="12"/>
-        <v>Elementos.de.AntiVibração</v>
+        <f t="shared" ref="T49:T51" si="15">SUBSTITUTE(D49, ".", " ")</f>
+        <v>Elementos de Climatização</v>
       </c>
       <c r="U49" s="39" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac.Dampers</v>
-      </c>
-      <c r="V49" s="39" t="s">
-        <v>232</v>
+        <f t="shared" ref="U49:U51" si="16">SUBSTITUTE(E49, ".", " ")</f>
+        <v>Avac Equipamentos Unitarios</v>
+      </c>
+      <c r="V49" s="38" t="s">
+        <v>490</v>
       </c>
       <c r="W49" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-49</v>
+        <v>Key-AVA-87</v>
       </c>
       <c r="X49" s="32" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="Y49" s="31" t="s">
-        <v>272</v>
+        <v>500</v>
       </c>
       <c r="Z49" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA49" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Damper typically participates in HVAC duct distribution system and is used to control or modulate.</v>
+        <v>Space heaters use a combination of natural radiation and/or convection.</v>
       </c>
     </row>
     <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="34">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>43</v>
@@ -8757,22 +9196,22 @@
       <c r="C50" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D50" s="35" t="s">
-        <v>464</v>
-      </c>
-      <c r="E50" s="35" t="s">
-        <v>422</v>
+      <c r="D50" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="F50" s="36" t="s">
-        <v>384</v>
+        <v>497</v>
       </c>
       <c r="G50" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H50" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I50" s="42" t="s">
+      <c r="H50" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I50" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J50" s="42" t="s">
@@ -8787,61 +9226,61 @@
       </c>
       <c r="M50" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.AntiVibração</v>
+        <v>Elementos.de.Climatização</v>
       </c>
       <c r="N50" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Dampers</v>
-      </c>
-      <c r="O50" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Avac.Vibração.Amortecedor</v>
+        <v>Avac Equipamentos Unitarios</v>
+      </c>
+      <c r="O50" s="37" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Aquecedor Convector</v>
       </c>
       <c r="P50" s="32" t="s">
-        <v>82</v>
+        <v>491</v>
       </c>
       <c r="Q50" s="32" t="s">
-        <v>130</v>
+        <v>492</v>
       </c>
       <c r="R50" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S50" s="39" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Climatização</v>
       </c>
       <c r="T50" s="39" t="str">
-        <f t="shared" si="12"/>
-        <v>Elementos.de.AntiVibração</v>
+        <f t="shared" si="15"/>
+        <v>Elementos de Climatização</v>
       </c>
       <c r="U50" s="39" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac.Dampers</v>
-      </c>
-      <c r="V50" s="39" t="s">
-        <v>232</v>
+        <f t="shared" si="16"/>
+        <v>Avac Equipamentos Unitarios</v>
+      </c>
+      <c r="V50" s="38" t="s">
+        <v>490</v>
       </c>
       <c r="W50" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-50</v>
+        <v>Key-AVA-88</v>
       </c>
       <c r="X50" s="32" t="s">
-        <v>271</v>
+        <v>499</v>
       </c>
       <c r="Y50" s="31" t="s">
-        <v>273</v>
+        <v>501</v>
       </c>
       <c r="Z50" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA50" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Vibration damper is a device used to minimize the effects of vibration on a structure.</v>
+        <v>Heat distribution unit that operates with air circulated by gravity.</v>
       </c>
     </row>
     <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="34">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>43</v>
@@ -8849,22 +9288,22 @@
       <c r="C51" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D51" s="35" t="s">
-        <v>464</v>
-      </c>
-      <c r="E51" s="35" t="s">
-        <v>422</v>
+      <c r="D51" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>495</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>385</v>
+        <v>498</v>
       </c>
       <c r="G51" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H51" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I51" s="42" t="s">
+      <c r="H51" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I51" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J51" s="42" t="s">
@@ -8879,61 +9318,61 @@
       </c>
       <c r="M51" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.AntiVibração</v>
+        <v>Elementos.de.Climatização</v>
       </c>
       <c r="N51" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Dampers</v>
-      </c>
-      <c r="O51" s="32" t="str">
-        <f t="shared" si="7"/>
-        <v>Avac.Vibração.Isolador</v>
+        <v>Avac Equipamentos Unitarios</v>
+      </c>
+      <c r="O51" s="37" t="str">
+        <f t="shared" si="13"/>
+        <v>Avac Aquecedor Radiação</v>
       </c>
       <c r="P51" s="32" t="s">
-        <v>83</v>
+        <v>493</v>
       </c>
       <c r="Q51" s="32" t="s">
-        <v>131</v>
+        <v>494</v>
       </c>
       <c r="R51" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S51" s="39" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="14"/>
         <v>Climatização</v>
       </c>
       <c r="T51" s="39" t="str">
-        <f t="shared" si="12"/>
-        <v>Elementos.de.AntiVibração</v>
+        <f t="shared" si="15"/>
+        <v>Elementos de Climatização</v>
       </c>
       <c r="U51" s="39" t="str">
-        <f t="shared" si="12"/>
-        <v>Avac.Dampers</v>
-      </c>
-      <c r="V51" s="39" t="s">
-        <v>232</v>
+        <f t="shared" si="16"/>
+        <v>Avac Equipamentos Unitarios</v>
+      </c>
+      <c r="V51" s="38" t="s">
+        <v>490</v>
       </c>
       <c r="W51" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-51</v>
+        <v>Key-AVA-89</v>
       </c>
       <c r="X51" s="32" t="s">
-        <v>274</v>
+        <v>499</v>
       </c>
       <c r="Y51" s="31" t="s">
-        <v>275</v>
+        <v>502</v>
       </c>
       <c r="Z51" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA51" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Vibration isolator is a device used to minimize the transmissibility effects of vibrations.</v>
+        <v>Heat distribution unit that operates with thermal radiation.</v>
       </c>
     </row>
     <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="34">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>43</v>
@@ -8941,14 +9380,14 @@
       <c r="C52" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D52" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E52" s="1" t="s">
-        <v>421</v>
+      <c r="D52" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E52" s="35" t="s">
+        <v>422</v>
       </c>
       <c r="F52" s="36" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="G52" s="42" t="s">
         <v>9</v>
@@ -8956,7 +9395,7 @@
       <c r="H52" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="I52" s="69" t="s">
+      <c r="I52" s="42" t="s">
         <v>9</v>
       </c>
       <c r="J52" s="42" t="s">
@@ -8971,61 +9410,61 @@
       </c>
       <c r="M52" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Sensorização</v>
+        <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="N52" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensores</v>
-      </c>
-      <c r="O52" s="37" t="str">
-        <f t="shared" si="9"/>
-        <v>Avac Sensor</v>
+        <v>Avac Dampers</v>
+      </c>
+      <c r="O52" s="32" t="str">
+        <f t="shared" si="7"/>
+        <v>Avac.Amortecedor</v>
       </c>
       <c r="P52" s="32" t="s">
-        <v>429</v>
+        <v>81</v>
       </c>
       <c r="Q52" s="32" t="s">
-        <v>302</v>
+        <v>129</v>
       </c>
       <c r="R52" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S52" s="39" t="str">
-        <f t="shared" ref="S52:U84" si="13">SUBSTITUTE(C52, ".", " ")</f>
+        <f t="shared" si="12"/>
         <v>Climatização</v>
       </c>
       <c r="T52" s="39" t="str">
-        <f t="shared" si="13"/>
-        <v>Elementos de Sensorização</v>
+        <f t="shared" si="12"/>
+        <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="U52" s="39" t="str">
-        <f t="shared" si="13"/>
-        <v>Avac Sensores</v>
+        <f t="shared" si="12"/>
+        <v>Avac.Dampers</v>
       </c>
       <c r="V52" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W52" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-52</v>
+        <v>Key-AVA-49</v>
       </c>
       <c r="X52" s="32" t="s">
-        <v>335</v>
+        <v>271</v>
       </c>
       <c r="Y52" s="31" t="s">
-        <v>336</v>
+        <v>272</v>
       </c>
       <c r="Z52" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA52" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A sensor is a device that measures a physical quantity and converts it into a signal that can be read. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>Damper typically participates in HVAC duct distribution system and is used to control or modulate.</v>
       </c>
     </row>
     <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="34">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>43</v>
@@ -9033,22 +9472,22 @@
       <c r="C53" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D53" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>421</v>
+      <c r="D53" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E53" s="35" t="s">
+        <v>422</v>
       </c>
       <c r="F53" s="36" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="G53" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H53" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I53" s="69" t="s">
+      <c r="H53" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="42" t="s">
         <v>9</v>
       </c>
       <c r="J53" s="42" t="s">
@@ -9063,61 +9502,61 @@
       </c>
       <c r="M53" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Sensorização</v>
+        <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="N53" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensores</v>
-      </c>
-      <c r="O53" s="37" t="str">
-        <f t="shared" si="9"/>
-        <v>Avac Sensor de Monóxido Carbono</v>
+        <v>Avac Dampers</v>
+      </c>
+      <c r="O53" s="32" t="str">
+        <f t="shared" si="7"/>
+        <v>Avac.Vibração.Amortecedor</v>
       </c>
       <c r="P53" s="32" t="s">
-        <v>430</v>
+        <v>82</v>
       </c>
       <c r="Q53" s="32" t="s">
-        <v>303</v>
+        <v>130</v>
       </c>
       <c r="R53" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S53" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Climatização</v>
       </c>
       <c r="T53" s="39" t="str">
-        <f t="shared" si="13"/>
-        <v>Elementos de Sensorização</v>
+        <f t="shared" si="12"/>
+        <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="U53" s="39" t="str">
-        <f t="shared" si="13"/>
-        <v>Avac Sensores</v>
+        <f t="shared" si="12"/>
+        <v>Avac.Dampers</v>
       </c>
       <c r="V53" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W53" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-53</v>
+        <v>Key-AVA-50</v>
       </c>
       <c r="X53" s="32" t="s">
-        <v>335</v>
+        <v>271</v>
       </c>
       <c r="Y53" s="31" t="s">
-        <v>337</v>
+        <v>273</v>
       </c>
       <c r="Z53" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA53" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that identifies or detects carbon monoxide. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>Vibration damper is a device used to minimize the effects of vibration on a structure.</v>
       </c>
     </row>
     <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="34">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>43</v>
@@ -9125,22 +9564,22 @@
       <c r="C54" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="D54" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>421</v>
+      <c r="D54" s="35" t="s">
+        <v>464</v>
+      </c>
+      <c r="E54" s="35" t="s">
+        <v>422</v>
       </c>
       <c r="F54" s="36" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="G54" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H54" s="69" t="s">
-        <v>9</v>
-      </c>
-      <c r="I54" s="69" t="s">
+      <c r="H54" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="I54" s="42" t="s">
         <v>9</v>
       </c>
       <c r="J54" s="42" t="s">
@@ -9155,61 +9594,61 @@
       </c>
       <c r="M54" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Sensorização</v>
+        <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="N54" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensores</v>
-      </c>
-      <c r="O54" s="37" t="str">
-        <f t="shared" si="9"/>
-        <v>Avac Sensor de Dióxido Carbono</v>
+        <v>Avac Dampers</v>
+      </c>
+      <c r="O54" s="32" t="str">
+        <f t="shared" si="7"/>
+        <v>Avac.Vibração.Isolador</v>
       </c>
       <c r="P54" s="32" t="s">
-        <v>431</v>
+        <v>83</v>
       </c>
       <c r="Q54" s="32" t="s">
-        <v>304</v>
+        <v>131</v>
       </c>
       <c r="R54" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S54" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="12"/>
         <v>Climatização</v>
       </c>
       <c r="T54" s="39" t="str">
-        <f t="shared" si="13"/>
-        <v>Elementos de Sensorização</v>
+        <f t="shared" si="12"/>
+        <v>Elementos.de.AntiVibração</v>
       </c>
       <c r="U54" s="39" t="str">
-        <f t="shared" si="13"/>
-        <v>Avac Sensores</v>
+        <f t="shared" si="12"/>
+        <v>Avac.Dampers</v>
       </c>
       <c r="V54" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W54" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-54</v>
+        <v>Key-AVA-51</v>
       </c>
       <c r="X54" s="32" t="s">
-        <v>335</v>
+        <v>274</v>
       </c>
       <c r="Y54" s="31" t="s">
-        <v>338</v>
+        <v>275</v>
       </c>
       <c r="Z54" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA54" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that identifies or detects carbon dioxide. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>Vibration isolator is a device used to minimize the transmissibility effects of vibrations.</v>
       </c>
     </row>
     <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="34">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>43</v>
@@ -9224,12 +9663,12 @@
         <v>421</v>
       </c>
       <c r="F55" s="36" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G55" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H55" s="69" t="s">
+      <c r="H55" s="42" t="s">
         <v>9</v>
       </c>
       <c r="I55" s="69" t="s">
@@ -9255,27 +9694,27 @@
       </c>
       <c r="O55" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensor de Condutância</v>
+        <v>Avac Sensor</v>
       </c>
       <c r="P55" s="32" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="Q55" s="32" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="R55" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S55" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" ref="S55:U87" si="17">SUBSTITUTE(C55, ".", " ")</f>
         <v>Climatização</v>
       </c>
       <c r="T55" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U55" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V55" s="39" t="s">
@@ -9283,25 +9722,25 @@
       </c>
       <c r="W55" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-55</v>
+        <v>Key-AVA-52</v>
       </c>
       <c r="X55" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y55" s="31" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="Z55" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA55" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that detects or detects electrical conductance. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A sensor is a device that measures a physical quantity and converts it into a signal that can be read. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="34">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>43</v>
@@ -9316,7 +9755,7 @@
         <v>421</v>
       </c>
       <c r="F56" s="36" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="G56" s="42" t="s">
         <v>9</v>
@@ -9347,27 +9786,27 @@
       </c>
       <c r="O56" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensor de Contato</v>
+        <v>Avac Sensor de Monóxido Carbono</v>
       </c>
       <c r="P56" s="32" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="Q56" s="32" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="R56" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S56" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T56" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U56" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V56" s="39" t="s">
@@ -9375,25 +9814,25 @@
       </c>
       <c r="W56" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-56</v>
+        <v>Key-AVA-53</v>
       </c>
       <c r="X56" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y56" s="31" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="Z56" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA56" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that senses or detects contact, such as to detect if a door is closed. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that identifies or detects carbon monoxide. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="34">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>43</v>
@@ -9408,7 +9847,7 @@
         <v>421</v>
       </c>
       <c r="F57" s="36" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="G57" s="42" t="s">
         <v>9</v>
@@ -9439,27 +9878,27 @@
       </c>
       <c r="O57" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensor de Sismos</v>
+        <v>Avac Sensor de Dióxido Carbono</v>
       </c>
       <c r="P57" s="32" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="Q57" s="32" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="R57" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S57" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T57" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U57" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V57" s="39" t="s">
@@ -9467,25 +9906,25 @@
       </c>
       <c r="W57" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-57</v>
+        <v>Key-AVA-54</v>
       </c>
       <c r="X57" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y57" s="31" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="Z57" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA57" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that senses or detects the seismic wave and measures the seismic intensity in the event of an earthquake. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that identifies or detects carbon dioxide. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="34">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>43</v>
@@ -9500,7 +9939,7 @@
         <v>421</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="G58" s="42" t="s">
         <v>9</v>
@@ -9531,27 +9970,27 @@
       </c>
       <c r="O58" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensor de Incêndio</v>
+        <v>Avac Sensor de Condutância</v>
       </c>
       <c r="P58" s="32" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="Q58" s="32" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="R58" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S58" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T58" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U58" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V58" s="39" t="s">
@@ -9559,25 +9998,25 @@
       </c>
       <c r="W58" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-58</v>
+        <v>Key-AVA-55</v>
       </c>
       <c r="X58" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y58" s="31" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="Z58" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA58" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Combined detector device (multi-criteria). It can detect the presence of heat, fire and smoke. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that detects or detects electrical conductance. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="34">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>43</v>
@@ -9592,7 +10031,7 @@
         <v>421</v>
       </c>
       <c r="F59" s="36" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="G59" s="42" t="s">
         <v>9</v>
@@ -9623,27 +10062,27 @@
       </c>
       <c r="O59" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensor de Fluxo</v>
+        <v>Avac Sensor de Contato</v>
       </c>
       <c r="P59" s="32" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="Q59" s="32" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="R59" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S59" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T59" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U59" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V59" s="39" t="s">
@@ -9651,25 +10090,25 @@
       </c>
       <c r="W59" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-59</v>
+        <v>Key-AVA-56</v>
       </c>
       <c r="X59" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y59" s="31" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="Z59" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA59" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that identifies or detects flow in a fluid. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that senses or detects contact, such as to detect if a door is closed. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="34">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>43</v>
@@ -9684,7 +10123,7 @@
         <v>421</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="G60" s="42" t="s">
         <v>9</v>
@@ -9715,27 +10154,27 @@
       </c>
       <c r="O60" s="37" t="str">
         <f t="shared" si="9"/>
-        <v>Avac Sensor de Detecção Objeto Estranho</v>
+        <v>Avac Sensor de Sismos</v>
       </c>
       <c r="P60" s="32" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="Q60" s="32" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="R60" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S60" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T60" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U60" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V60" s="39" t="s">
@@ -9743,25 +10182,25 @@
       </c>
       <c r="W60" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-60</v>
+        <v>Key-AVA-57</v>
       </c>
       <c r="X60" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y60" s="31" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="Z60" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA60" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that senses or detects foreign objects that interfere with the power grid. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that senses or detects the seismic wave and measures the seismic intensity in the event of an earthquake. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="34">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>43</v>
@@ -9776,7 +10215,7 @@
         <v>421</v>
       </c>
       <c r="F61" s="36" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="G61" s="42" t="s">
         <v>9</v>
@@ -9802,32 +10241,32 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N61" s="37" t="str">
-        <f t="shared" ref="N61:O86" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E61),"."," ")," De "," de "))</f>
+        <f t="shared" si="9"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O61" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Geada</v>
+        <f t="shared" si="9"/>
+        <v>Avac Sensor de Incêndio</v>
       </c>
       <c r="P61" s="32" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="Q61" s="32" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="R61" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S61" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T61" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U61" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V61" s="39" t="s">
@@ -9835,25 +10274,25 @@
       </c>
       <c r="W61" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-61</v>
+        <v>Key-AVA-58</v>
       </c>
       <c r="X61" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y61" s="31" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="Z61" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA61" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Device that identifies or detects freezing in a window. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>Combined detector device (multi-criteria). It can detect the presence of heat, fire and smoke. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="34">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B62" s="1" t="s">
         <v>43</v>
@@ -9868,7 +10307,7 @@
         <v>421</v>
       </c>
       <c r="F62" s="36" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="G62" s="42" t="s">
         <v>9</v>
@@ -9894,32 +10333,32 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N62" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O62" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Gás</v>
+        <f t="shared" si="9"/>
+        <v>Avac Sensor de Fluxo</v>
       </c>
       <c r="P62" s="32" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="Q62" s="32" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="R62" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S62" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T62" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U62" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V62" s="39" t="s">
@@ -9927,25 +10366,25 @@
       </c>
       <c r="W62" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-62</v>
+        <v>Key-AVA-59</v>
       </c>
       <c r="X62" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y62" s="31" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="Z62" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA62" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that detects or detects gas concentration (except CO2). Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that identifies or detects flow in a fluid. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="34">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>43</v>
@@ -9960,7 +10399,7 @@
         <v>421</v>
       </c>
       <c r="F63" s="36" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="G63" s="42" t="s">
         <v>9</v>
@@ -9986,32 +10425,32 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N63" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="9"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O63" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Calor</v>
+        <f t="shared" si="9"/>
+        <v>Avac Sensor de Detecção Objeto Estranho</v>
       </c>
       <c r="P63" s="32" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="Q63" s="32" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="R63" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S63" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T63" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U63" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V63" s="39" t="s">
@@ -10019,25 +10458,25 @@
       </c>
       <c r="W63" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-63</v>
+        <v>Key-AVA-60</v>
       </c>
       <c r="X63" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y63" s="31" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="Z63" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA63" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that identifies or detects heat. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that senses or detects foreign objects that interfere with the power grid. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="34">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>43</v>
@@ -10052,7 +10491,7 @@
         <v>421</v>
       </c>
       <c r="F64" s="36" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="G64" s="42" t="s">
         <v>9</v>
@@ -10078,32 +10517,32 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N64" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" ref="N64:O89" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E64),"."," ")," De "," de "))</f>
         <v>Avac Sensores</v>
       </c>
       <c r="O64" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Umidade</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Geada</v>
       </c>
       <c r="P64" s="32" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="Q64" s="32" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R64" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S64" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T64" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U64" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V64" s="39" t="s">
@@ -10111,25 +10550,25 @@
       </c>
       <c r="W64" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-64</v>
+        <v>Key-AVA-61</v>
       </c>
       <c r="X64" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y64" s="31" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="Z64" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA64" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>Device that identifies or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>Device that identifies or detects freezing in a window. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="34">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>43</v>
@@ -10144,7 +10583,7 @@
         <v>421</v>
       </c>
       <c r="F65" s="36" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="G65" s="42" t="s">
         <v>9</v>
@@ -10170,32 +10609,32 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N65" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O65" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Identificação</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Gás</v>
       </c>
       <c r="P65" s="32" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="Q65" s="32" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="R65" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S65" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T65" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U65" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V65" s="39" t="s">
@@ -10203,25 +10642,25 @@
       </c>
       <c r="W65" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-65</v>
+        <v>Key-AVA-62</v>
       </c>
       <c r="X65" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y65" s="31" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="Z65" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA65" s="32" t="str">
         <f t="shared" si="3"/>
-        <v>A device that reads a label, such as to gain access to a door or elevator. Verify (MQTT) message queuing telemetry transport.</v>
+        <v>A device that detects or detects gas concentration (except CO2). Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="34">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>43</v>
@@ -10236,7 +10675,7 @@
         <v>421</v>
       </c>
       <c r="F66" s="36" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="G66" s="42" t="s">
         <v>9</v>
@@ -10262,32 +10701,32 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N66" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O66" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Concentração de Íons</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Calor</v>
       </c>
       <c r="P66" s="32" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q66" s="32" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="R66" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S66" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T66" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U66" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V66" s="39" t="s">
@@ -10295,25 +10734,25 @@
       </c>
       <c r="W66" s="68" t="str">
         <f t="shared" si="4"/>
-        <v>Key-AVA-66</v>
+        <v>Key-AVA-63</v>
       </c>
       <c r="X66" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y66" s="31" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="Z66" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA66" s="32" t="str">
-        <f t="shared" ref="AA66:AA86" si="15">_xlfn.TRANSLATE(P66,"pt","en")</f>
-        <v>A device that senses or detects the concentration of ion, such as to measure the hardness of water. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="3"/>
+        <v>A device that identifies or detects heat. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="34">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>43</v>
@@ -10328,7 +10767,7 @@
         <v>421</v>
       </c>
       <c r="F67" s="36" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="G67" s="42" t="s">
         <v>9</v>
@@ -10354,58 +10793,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N67" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O67" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Nível</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Umidade</v>
       </c>
       <c r="P67" s="32" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="Q67" s="32" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="R67" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S67" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T67" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U67" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V67" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W67" s="68" t="str">
-        <f t="shared" ref="W67:W86" si="16">CONCATENATE("Key-AVA-",A67)</f>
-        <v>Key-AVA-67</v>
+        <f t="shared" si="4"/>
+        <v>Key-AVA-64</v>
       </c>
       <c r="X67" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y67" s="31" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="Z67" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA67" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that senses or detects the fill level, such as for a tank. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="3"/>
+        <v>Device that identifies or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="34">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B68" s="1" t="s">
         <v>43</v>
@@ -10420,7 +10859,7 @@
         <v>421</v>
       </c>
       <c r="F68" s="36" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="G68" s="42" t="s">
         <v>9</v>
@@ -10446,58 +10885,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N68" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O68" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Luz</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Identificação</v>
       </c>
       <c r="P68" s="32" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="Q68" s="32" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="R68" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S68" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T68" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U68" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V68" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W68" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-68</v>
+        <f t="shared" si="4"/>
+        <v>Key-AVA-65</v>
       </c>
       <c r="X68" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y68" s="31" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="Z68" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA68" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that identifies or detects light. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="3"/>
+        <v>A device that reads a label, such as to gain access to a door or elevator. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="34">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>43</v>
@@ -10512,7 +10951,7 @@
         <v>421</v>
       </c>
       <c r="F69" s="36" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="G69" s="42" t="s">
         <v>9</v>
@@ -10538,58 +10977,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N69" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O69" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Umidade do Solo</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Concentração de Íons</v>
       </c>
       <c r="P69" s="32" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="Q69" s="32" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="R69" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S69" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T69" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U69" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V69" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W69" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-69</v>
+        <f t="shared" si="4"/>
+        <v>Key-AVA-66</v>
       </c>
       <c r="X69" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y69" s="31" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="Z69" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA69" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Device that senses or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" ref="AA69:AA89" si="19">_xlfn.TRANSLATE(P69,"pt","en")</f>
+        <v>A device that senses or detects the concentration of ion, such as to measure the hardness of water. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="34">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>43</v>
@@ -10604,7 +11043,7 @@
         <v>421</v>
       </c>
       <c r="F70" s="36" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="G70" s="42" t="s">
         <v>9</v>
@@ -10630,58 +11069,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N70" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O70" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Movimento</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Nível</v>
       </c>
       <c r="P70" s="32" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="Q70" s="32" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="R70" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S70" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T70" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U70" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V70" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W70" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-70</v>
+        <f t="shared" ref="W70:W89" si="20">CONCATENATE("Key-AVA-",A70)</f>
+        <v>Key-AVA-67</v>
       </c>
       <c r="X70" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y70" s="31" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="Z70" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA70" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that identifies or detects motion. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that senses or detects the fill level, such as for a tank. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="34">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>43</v>
@@ -10696,7 +11135,7 @@
         <v>421</v>
       </c>
       <c r="F71" s="36" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G71" s="42" t="s">
         <v>9</v>
@@ -10722,58 +11161,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N71" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O71" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Obstáculo</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Luz</v>
       </c>
       <c r="P71" s="32" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
       <c r="Q71" s="32" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="R71" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S71" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T71" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U71" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V71" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W71" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-71</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-68</v>
       </c>
       <c r="X71" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y71" s="31" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="Z71" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA71" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Device that detects or detects any obstacles. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that identifies or detects light. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="34">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>43</v>
@@ -10788,7 +11227,7 @@
         <v>421</v>
       </c>
       <c r="F72" s="36" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="G72" s="42" t="s">
         <v>9</v>
@@ -10814,58 +11253,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N72" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O72" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de pH</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Umidade do Solo</v>
       </c>
       <c r="P72" s="32" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="Q72" s="32" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="R72" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S72" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T72" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U72" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V72" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W72" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-72</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-69</v>
       </c>
       <c r="X72" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y72" s="31" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="Z72" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA72" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Device that identifies or detects acidity. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>Device that senses or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="34">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="B73" s="1" t="s">
         <v>43</v>
@@ -10880,7 +11319,7 @@
         <v>421</v>
       </c>
       <c r="F73" s="36" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="G73" s="42" t="s">
         <v>9</v>
@@ -10906,58 +11345,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N73" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O73" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Pressão</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Movimento</v>
       </c>
       <c r="P73" s="32" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="Q73" s="32" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="R73" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S73" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T73" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U73" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V73" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W73" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-73</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-70</v>
       </c>
       <c r="X73" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y73" s="31" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="Z73" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA73" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Device that senses or senses pressure. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that identifies or detects motion. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="34">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>43</v>
@@ -10972,7 +11411,7 @@
         <v>421</v>
       </c>
       <c r="F74" s="36" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="G74" s="42" t="s">
         <v>9</v>
@@ -10998,58 +11437,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N74" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O74" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Radiação</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Obstáculo</v>
       </c>
       <c r="P74" s="32" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="Q74" s="32" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="R74" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S74" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T74" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U74" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V74" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W74" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-74</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-71</v>
       </c>
       <c r="X74" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y74" s="31" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="Z74" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA74" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that senses or detects radiation. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>Device that detects or detects any obstacles. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="34">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>43</v>
@@ -11064,7 +11503,7 @@
         <v>421</v>
       </c>
       <c r="F75" s="36" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="G75" s="42" t="s">
         <v>9</v>
@@ -11090,58 +11529,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N75" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O75" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Radioatividade</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de pH</v>
       </c>
       <c r="P75" s="32" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="Q75" s="32" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="R75" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S75" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T75" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U75" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V75" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W75" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-75</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-72</v>
       </c>
       <c r="X75" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y75" s="31" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="Z75" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA75" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that senses or detects atomic decay. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>Device that identifies or detects acidity. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="34">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>43</v>
@@ -11156,7 +11595,7 @@
         <v>421</v>
       </c>
       <c r="F76" s="36" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="G76" s="42" t="s">
         <v>9</v>
@@ -11182,58 +11621,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N76" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O76" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Chuva</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Pressão</v>
       </c>
       <c r="P76" s="32" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="Q76" s="32" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="R76" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S76" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T76" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U76" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V76" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W76" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-76</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-73</v>
       </c>
       <c r="X76" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y76" s="31" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="Z76" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA76" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that perceives or collects information related to rainfall. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>Device that senses or senses pressure. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="34">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>43</v>
@@ -11248,7 +11687,7 @@
         <v>421</v>
       </c>
       <c r="F77" s="36" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="G77" s="42" t="s">
         <v>9</v>
@@ -11274,58 +11713,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N77" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O77" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Fumaça</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Radiação</v>
       </c>
       <c r="P77" s="32" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="Q77" s="32" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="R77" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S77" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T77" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U77" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V77" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W77" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-77</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-74</v>
       </c>
       <c r="X77" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y77" s="31" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="Z77" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA77" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Device that identifies or detects smoke. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that senses or detects radiation. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="34">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B78" s="1" t="s">
         <v>43</v>
@@ -11340,7 +11779,7 @@
         <v>421</v>
       </c>
       <c r="F78" s="36" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="G78" s="42" t="s">
         <v>9</v>
@@ -11366,58 +11805,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N78" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O78" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Profundidade da Neve</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Radioatividade</v>
       </c>
       <c r="P78" s="32" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="Q78" s="32" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="R78" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S78" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T78" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U78" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V78" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W78" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-78</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-75</v>
       </c>
       <c r="X78" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y78" s="31" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="Z78" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA78" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that perceives or measures the depth of accumulated snow. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that senses or detects atomic decay. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="34">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B79" s="1" t="s">
         <v>43</v>
@@ -11432,7 +11871,7 @@
         <v>421</v>
       </c>
       <c r="F79" s="36" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="G79" s="42" t="s">
         <v>9</v>
@@ -11458,58 +11897,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N79" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O79" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Som</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Chuva</v>
       </c>
       <c r="P79" s="32" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="Q79" s="32" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="R79" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S79" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T79" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U79" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V79" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W79" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-79</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-76</v>
       </c>
       <c r="X79" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y79" s="31" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="Z79" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA79" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that identifies or detects sound. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that perceives or collects information related to rainfall. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="34">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>43</v>
@@ -11524,7 +11963,7 @@
         <v>421</v>
       </c>
       <c r="F80" s="36" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="G80" s="42" t="s">
         <v>9</v>
@@ -11550,58 +11989,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N80" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O80" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Temperatura</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Fumaça</v>
       </c>
       <c r="P80" s="32" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="Q80" s="32" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="R80" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S80" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T80" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U80" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V80" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W80" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-80</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-77</v>
       </c>
       <c r="X80" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y80" s="31" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="Z80" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA80" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>Device that identifies or detects temperature. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>Device that identifies or detects smoke. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="34">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>43</v>
@@ -11616,7 +12055,7 @@
         <v>421</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="G81" s="42" t="s">
         <v>9</v>
@@ -11642,58 +12081,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N81" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O81" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Trem</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Profundidade da Neve</v>
       </c>
       <c r="P81" s="32" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="Q81" s="32" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="R81" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S81" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T81" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U81" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V81" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W81" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-81</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-78</v>
       </c>
       <c r="X81" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y81" s="31" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="Z81" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA81" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that is placed at the rear end of the last car of a train acting on a fixed equipment. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that perceives or measures the depth of accumulated snow. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="34">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>43</v>
@@ -11708,7 +12147,7 @@
         <v>421</v>
       </c>
       <c r="F82" s="36" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="G82" s="42" t="s">
         <v>9</v>
@@ -11734,58 +12173,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N82" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O82" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Desvio Ferroviário</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Som</v>
       </c>
       <c r="P82" s="32" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="Q82" s="32" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="R82" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S82" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T82" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U82" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V82" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W82" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-82</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-79</v>
       </c>
       <c r="X82" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y82" s="31" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="Z82" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA82" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that detects or detects the position of a blade of an AMV. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that identifies or detects sound. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="34">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>43</v>
@@ -11800,7 +12239,7 @@
         <v>421</v>
       </c>
       <c r="F83" s="36" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="G83" s="42" t="s">
         <v>9</v>
@@ -11826,58 +12265,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N83" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O83" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Roda</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Temperatura</v>
       </c>
       <c r="P83" s="32" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="Q83" s="32" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="R83" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S83" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T83" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U83" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V83" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W83" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-83</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-80</v>
       </c>
       <c r="X83" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y83" s="31" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Z83" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA83" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that senses or detects the passage of a wheel. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>Device that identifies or detects temperature. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="34">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>43</v>
@@ -11892,7 +12331,7 @@
         <v>421</v>
       </c>
       <c r="F84" s="36" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="G84" s="42" t="s">
         <v>9</v>
@@ -11918,58 +12357,58 @@
         <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N84" s="37" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="18"/>
         <v>Avac Sensores</v>
       </c>
       <c r="O84" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Sensor de Vento</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Trem</v>
       </c>
       <c r="P84" s="32" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="Q84" s="32" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="R84" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S84" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T84" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Elementos de Sensorização</v>
       </c>
       <c r="U84" s="39" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="17"/>
         <v>Avac Sensores</v>
       </c>
       <c r="V84" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W84" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-84</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-81</v>
       </c>
       <c r="X84" s="32" t="s">
         <v>335</v>
       </c>
       <c r="Y84" s="31" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="Z84" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA84" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>A device that perceives or senses the speed and direction of airflow. Verify (MQTT) message queuing telemetry transport.</v>
+        <f t="shared" si="19"/>
+        <v>A device that is placed at the rear end of the last car of a train acting on a fixed equipment. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="34">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>43</v>
@@ -11978,21 +12417,21 @@
         <v>482</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F85" s="40" t="s">
-        <v>419</v>
+        <v>421</v>
+      </c>
+      <c r="F85" s="36" t="s">
+        <v>416</v>
       </c>
       <c r="G85" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H85" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I85" s="42" t="s">
+      <c r="H85" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I85" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J85" s="42" t="s">
@@ -12007,61 +12446,61 @@
       </c>
       <c r="M85" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Acessórios</v>
+        <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N85" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Acessórios</v>
-      </c>
-      <c r="O85" s="32" t="str">
-        <f>IF(ISNUMBER(FIND("Ifc",F85)),CONCATENATE("",F85),CONCATENATE("",F85))</f>
-        <v>Avac.Acessório.Duto.Avac</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O85" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Desvio Ferroviário</v>
       </c>
       <c r="P85" s="32" t="s">
-        <v>194</v>
+        <v>461</v>
       </c>
       <c r="Q85" s="32" t="s">
-        <v>196</v>
+        <v>332</v>
       </c>
       <c r="R85" s="38" t="s">
         <v>9</v>
       </c>
       <c r="S85" s="39" t="str">
-        <f t="shared" ref="S85:U86" si="17">SUBSTITUTE(C85, "_", " ")</f>
+        <f t="shared" si="17"/>
         <v>Climatização</v>
       </c>
       <c r="T85" s="39" t="str">
         <f t="shared" si="17"/>
-        <v>Elementos.de.Acessórios</v>
+        <v>Elementos de Sensorização</v>
       </c>
       <c r="U85" s="39" t="str">
         <f t="shared" si="17"/>
-        <v>Avac.Acessórios</v>
+        <v>Avac Sensores</v>
       </c>
       <c r="V85" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W85" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-85</v>
-      </c>
-      <c r="X85" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="Y85" s="32" t="s">
-        <v>234</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-82</v>
+      </c>
+      <c r="X85" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y85" s="31" t="s">
+        <v>366</v>
       </c>
       <c r="Z85" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA85" s="32" t="str">
-        <f t="shared" si="15"/>
-        <v>HVAC duct accessories.</v>
+        <f t="shared" si="19"/>
+        <v>A device that detects or detects the position of a blade of an AMV. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
     <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="34">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>43</v>
@@ -12070,21 +12509,21 @@
         <v>482</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>487</v>
+        <v>465</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>423</v>
-      </c>
-      <c r="F86" s="1" t="s">
-        <v>420</v>
+        <v>421</v>
+      </c>
+      <c r="F86" s="36" t="s">
+        <v>417</v>
       </c>
       <c r="G86" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="H86" s="42" t="s">
-        <v>9</v>
-      </c>
-      <c r="I86" s="42" t="s">
+      <c r="H86" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I86" s="69" t="s">
         <v>9</v>
       </c>
       <c r="J86" s="42" t="s">
@@ -12099,21 +12538,21 @@
       </c>
       <c r="M86" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Elementos.de.Acessórios</v>
+        <v>Elementos.de.Sensorização</v>
       </c>
       <c r="N86" s="37" t="str">
-        <f t="shared" si="14"/>
-        <v>Avac Acessórios</v>
-      </c>
-      <c r="O86" s="32" t="str">
-        <f t="shared" ref="O86" si="18">IF(ISNUMBER(FIND("Ifc",F86)),CONCATENATE("",F86),CONCATENATE("",F86))</f>
-        <v>Avac.Acessório.Tubo.Avac</v>
+        <f t="shared" si="18"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O86" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Roda</v>
       </c>
       <c r="P86" s="32" t="s">
-        <v>195</v>
+        <v>459</v>
       </c>
       <c r="Q86" s="32" t="s">
-        <v>197</v>
+        <v>333</v>
       </c>
       <c r="R86" s="38" t="s">
         <v>9</v>
@@ -12124,148 +12563,443 @@
       </c>
       <c r="T86" s="39" t="str">
         <f t="shared" si="17"/>
-        <v>Elementos.de.Acessórios</v>
+        <v>Elementos de Sensorização</v>
       </c>
       <c r="U86" s="39" t="str">
         <f t="shared" si="17"/>
-        <v>Avac.Acessórios</v>
+        <v>Avac Sensores</v>
       </c>
       <c r="V86" s="39" t="s">
         <v>232</v>
       </c>
       <c r="W86" s="68" t="str">
-        <f t="shared" si="16"/>
-        <v>Key-AVA-86</v>
+        <f t="shared" si="20"/>
+        <v>Key-AVA-83</v>
       </c>
       <c r="X86" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="Y86" s="32" t="s">
-        <v>234</v>
+        <v>335</v>
+      </c>
+      <c r="Y86" s="31" t="s">
+        <v>367</v>
       </c>
       <c r="Z86" s="38" t="s">
         <v>287</v>
       </c>
       <c r="AA86" s="32" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
+        <v>A device that senses or detects the passage of a wheel. Verify (MQTT) message queuing telemetry transport.</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="34">
+        <v>84</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C87" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="F87" s="36" t="s">
+        <v>418</v>
+      </c>
+      <c r="G87" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="I87" s="69" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="K87" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="L87" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Climatização</v>
+      </c>
+      <c r="M87" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Elementos.de.Sensorização</v>
+      </c>
+      <c r="N87" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="O87" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Avac Sensor de Vento</v>
+      </c>
+      <c r="P87" s="32" t="s">
+        <v>460</v>
+      </c>
+      <c r="Q87" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="R87" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="S87" s="39" t="str">
+        <f t="shared" si="17"/>
+        <v>Climatização</v>
+      </c>
+      <c r="T87" s="39" t="str">
+        <f t="shared" si="17"/>
+        <v>Elementos de Sensorização</v>
+      </c>
+      <c r="U87" s="39" t="str">
+        <f t="shared" si="17"/>
+        <v>Avac Sensores</v>
+      </c>
+      <c r="V87" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="W87" s="68" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-AVA-84</v>
+      </c>
+      <c r="X87" s="32" t="s">
+        <v>335</v>
+      </c>
+      <c r="Y87" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="Z87" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA87" s="32" t="str">
+        <f t="shared" si="19"/>
+        <v>A device that perceives or senses the speed and direction of airflow. Verify (MQTT) message queuing telemetry transport.</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A88" s="34">
+        <v>85</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F88" s="40" t="s">
+        <v>419</v>
+      </c>
+      <c r="G88" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H88" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="I88" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="K88" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="L88" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Climatização</v>
+      </c>
+      <c r="M88" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Elementos.de.Acessórios</v>
+      </c>
+      <c r="N88" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Avac Acessórios</v>
+      </c>
+      <c r="O88" s="32" t="str">
+        <f>IF(ISNUMBER(FIND("Ifc",F88)),CONCATENATE("",F88),CONCATENATE("",F88))</f>
+        <v>Avac.Acessório.Duto.Avac</v>
+      </c>
+      <c r="P88" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="Q88" s="32" t="s">
+        <v>196</v>
+      </c>
+      <c r="R88" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="S88" s="39" t="str">
+        <f t="shared" ref="S88:U89" si="21">SUBSTITUTE(C88, "_", " ")</f>
+        <v>Climatização</v>
+      </c>
+      <c r="T88" s="39" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos.de.Acessórios</v>
+      </c>
+      <c r="U88" s="39" t="str">
+        <f t="shared" si="21"/>
+        <v>Avac.Acessórios</v>
+      </c>
+      <c r="V88" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="W88" s="68" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-AVA-85</v>
+      </c>
+      <c r="X88" s="39" t="s">
+        <v>233</v>
+      </c>
+      <c r="Y88" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z88" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA88" s="32" t="str">
+        <f t="shared" si="19"/>
+        <v>HVAC duct accessories.</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A89" s="34">
+        <v>86</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="E89" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="G89" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="H89" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="I89" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="K89" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="L89" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Climatização</v>
+      </c>
+      <c r="M89" s="37" t="str">
+        <f t="shared" si="11"/>
+        <v>Elementos.de.Acessórios</v>
+      </c>
+      <c r="N89" s="37" t="str">
+        <f t="shared" si="18"/>
+        <v>Avac Acessórios</v>
+      </c>
+      <c r="O89" s="32" t="str">
+        <f t="shared" ref="O89" si="22">IF(ISNUMBER(FIND("Ifc",F89)),CONCATENATE("",F89),CONCATENATE("",F89))</f>
+        <v>Avac.Acessório.Tubo.Avac</v>
+      </c>
+      <c r="P89" s="32" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q89" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="R89" s="38" t="s">
+        <v>9</v>
+      </c>
+      <c r="S89" s="39" t="str">
+        <f t="shared" si="21"/>
+        <v>Climatização</v>
+      </c>
+      <c r="T89" s="39" t="str">
+        <f t="shared" si="21"/>
+        <v>Elementos.de.Acessórios</v>
+      </c>
+      <c r="U89" s="39" t="str">
+        <f t="shared" si="21"/>
+        <v>Avac.Acessórios</v>
+      </c>
+      <c r="V89" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="W89" s="68" t="str">
+        <f t="shared" si="20"/>
+        <v>Key-AVA-86</v>
+      </c>
+      <c r="X89" s="32" t="s">
+        <v>235</v>
+      </c>
+      <c r="Y89" s="32" t="s">
+        <v>234</v>
+      </c>
+      <c r="Z89" s="38" t="s">
+        <v>287</v>
+      </c>
+      <c r="AA89" s="32" t="str">
+        <f t="shared" si="19"/>
         <v>HVAC pipe segments.</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="99" priority="64" operator="equal">
+  <conditionalFormatting sqref="A2:A89">
+    <cfRule type="cellIs" dxfId="110" priority="26" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="98" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="62"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6">
-    <cfRule type="cellIs" dxfId="94" priority="63" operator="equal">
+  <conditionalFormatting sqref="D55:F87 L55:Q87 S55:U87 X55:Y87 E88:E89">
+    <cfRule type="cellIs" dxfId="109" priority="30" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F6 F87:F1048576">
-    <cfRule type="duplicateValues" dxfId="93" priority="39"/>
+  <conditionalFormatting sqref="F1">
+    <cfRule type="duplicateValues" dxfId="108" priority="2313"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="92" priority="2289"/>
+  <conditionalFormatting sqref="F90:F1048576 F1:F6">
+    <cfRule type="duplicateValues" dxfId="107" priority="63"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F87:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="42" priority="2291"/>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="duplicateValues" dxfId="106" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="86"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F87:F1048576">
-    <cfRule type="duplicateValues" dxfId="41" priority="2294"/>
+  <conditionalFormatting sqref="F7:F9">
+    <cfRule type="duplicateValues" dxfId="102" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="27"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F87:F1048576">
-    <cfRule type="duplicateValues" dxfId="40" priority="2296"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="2297"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="2298"/>
+  <conditionalFormatting sqref="F10:F20">
+    <cfRule type="duplicateValues" dxfId="100" priority="58"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A10:A86 AA10:AA86">
-    <cfRule type="cellIs" dxfId="37" priority="14" operator="equal">
+  <conditionalFormatting sqref="F10:F48 F52:F89">
+    <cfRule type="duplicateValues" dxfId="99" priority="28"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21:F22 F88:F89">
+    <cfRule type="duplicateValues" dxfId="98" priority="48"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F21:F22">
+    <cfRule type="duplicateValues" dxfId="97" priority="57"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F23:F29">
+    <cfRule type="duplicateValues" dxfId="96" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="62"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F30:F31">
+    <cfRule type="duplicateValues" dxfId="92" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="40"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:F33">
+    <cfRule type="duplicateValues" dxfId="90" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="47"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F32:F48">
+    <cfRule type="duplicateValues" dxfId="86" priority="42"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F34:F48">
+    <cfRule type="duplicateValues" dxfId="85" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="43"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F52:F54">
+    <cfRule type="duplicateValues" dxfId="83" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="56"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F55:F87">
+    <cfRule type="duplicateValues" dxfId="76" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="35"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F88:F89 F10:F48 F52:F54">
+    <cfRule type="duplicateValues" dxfId="70" priority="37"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F88:F89 F21:F31">
+    <cfRule type="duplicateValues" dxfId="69" priority="49"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F88:F89">
+    <cfRule type="duplicateValues" dxfId="68" priority="36"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F90:F1048576 F1">
+    <cfRule type="duplicateValues" dxfId="67" priority="2315"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F90:F1048576">
+    <cfRule type="duplicateValues" dxfId="66" priority="2318"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="2320"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="2321"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="2322"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA6">
+    <cfRule type="cellIs" dxfId="62" priority="87" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D52:F84 L52:Q84 S52:U84 X52:Y84 E85:E86">
-    <cfRule type="cellIs" dxfId="36" priority="6" operator="equal">
+  <conditionalFormatting sqref="AA10:AA48 AA52:AA89">
+    <cfRule type="cellIs" dxfId="61" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F20">
-    <cfRule type="duplicateValues" dxfId="35" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F22">
-    <cfRule type="duplicateValues" dxfId="34" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F23:F29">
-    <cfRule type="duplicateValues" dxfId="33" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="29" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32:F33">
-    <cfRule type="duplicateValues" dxfId="27" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F32:F48">
-    <cfRule type="duplicateValues" dxfId="23" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F34:F48">
-    <cfRule type="duplicateValues" dxfId="22" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F49:F51">
-    <cfRule type="duplicateValues" dxfId="20" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F52:F84">
-    <cfRule type="duplicateValues" dxfId="13" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F85:F86">
-    <cfRule type="duplicateValues" dxfId="7" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F85:F86 F10:F51">
-    <cfRule type="duplicateValues" dxfId="6" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F22 F85:F86">
-    <cfRule type="duplicateValues" dxfId="5" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F85:F86 F21:F31">
-    <cfRule type="duplicateValues" dxfId="4" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F10:F86">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:A9">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+  <conditionalFormatting sqref="B49:B51 L49:Q51 F49:F51 S49:V51 X49:Y51 AA49:XFD51">
+    <cfRule type="cellIs" dxfId="60" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  <conditionalFormatting sqref="F49:F51">
+    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="8"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="F49:F51">
+    <cfRule type="duplicateValues" dxfId="53" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49:F51">
+    <cfRule type="duplicateValues" dxfId="52" priority="9"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49:F51">
+    <cfRule type="duplicateValues" dxfId="51" priority="10"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F49:F51">
+    <cfRule type="duplicateValues" dxfId="50" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="duplicateValues" dxfId="49" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15559,7 +16293,7 @@
         <v>9</v>
       </c>
       <c r="S36" s="39" t="str">
-        <f t="shared" ref="S36:U66" si="14">SUBSTITUTE(C36, "_", " ")</f>
+        <f t="shared" ref="S36:U45" si="14">SUBSTITUTE(C36, "_", " ")</f>
         <v>Climatização</v>
       </c>
       <c r="T36" s="39" t="str">
@@ -19640,87 +20374,85 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A4:A80 AA4:AA80">
-    <cfRule type="cellIs" dxfId="91" priority="14" operator="equal">
+  <conditionalFormatting sqref="A1:A80">
+    <cfRule type="cellIs" dxfId="48" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D46:F78 L46:Q78 S46:U78 X46:Y78 AB46:XFD78 E79:E80">
-    <cfRule type="cellIs" dxfId="90" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F14">
-    <cfRule type="duplicateValues" dxfId="89" priority="34"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F16">
-    <cfRule type="duplicateValues" dxfId="88" priority="33"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F17:F23">
-    <cfRule type="duplicateValues" dxfId="87" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="38"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F25">
-    <cfRule type="duplicateValues" dxfId="83" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="16"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F27">
-    <cfRule type="duplicateValues" dxfId="81" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="23"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F26:F42">
-    <cfRule type="duplicateValues" dxfId="77" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F28:F42">
-    <cfRule type="duplicateValues" dxfId="76" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="19"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F43:F45">
-    <cfRule type="duplicateValues" dxfId="74" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="32"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F46:F78">
-    <cfRule type="duplicateValues" dxfId="67" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="11"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F79:F80">
-    <cfRule type="duplicateValues" dxfId="61" priority="12"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F79:F80 F4:F45">
-    <cfRule type="duplicateValues" dxfId="60" priority="13"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F15:F16 F79:F80">
-    <cfRule type="duplicateValues" dxfId="59" priority="24"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F79:F80 F15:F25">
-    <cfRule type="duplicateValues" dxfId="58" priority="25"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F4:F80">
-    <cfRule type="duplicateValues" dxfId="57" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A1:A3">
-    <cfRule type="cellIs" dxfId="56" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="47" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F3">
-    <cfRule type="duplicateValues" dxfId="55" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F3">
-    <cfRule type="duplicateValues" dxfId="54" priority="1"/>
+  <conditionalFormatting sqref="F4:F14">
+    <cfRule type="duplicateValues" dxfId="44" priority="34"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F4:F80">
+    <cfRule type="duplicateValues" dxfId="43" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F16 F79:F80">
+    <cfRule type="duplicateValues" dxfId="42" priority="24"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:F16">
+    <cfRule type="duplicateValues" dxfId="41" priority="33"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F17:F23">
+    <cfRule type="duplicateValues" dxfId="40" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="38"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F25">
+    <cfRule type="duplicateValues" dxfId="36" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="16"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:F27">
+    <cfRule type="duplicateValues" dxfId="34" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="23"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26:F42">
+    <cfRule type="duplicateValues" dxfId="30" priority="18"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F28:F42">
+    <cfRule type="duplicateValues" dxfId="29" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F43:F45">
+    <cfRule type="duplicateValues" dxfId="27" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="32"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F46:F78">
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F79:F80 F4:F45">
+    <cfRule type="duplicateValues" dxfId="14" priority="13"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F79:F80 F15:F25">
+    <cfRule type="duplicateValues" dxfId="13" priority="25"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F79:F80">
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA4:AA80">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -19935,7 +20667,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="53" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20008,22 +20740,22 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="52" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:G1 C2:G2">
-    <cfRule type="containsText" dxfId="51" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="8" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="50" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576">
-    <cfRule type="duplicateValues" dxfId="49" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:G1048576">
-    <cfRule type="containsText" dxfId="47" priority="8" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="4" priority="8" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -20710,20 +21442,20 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="duplicateValues" dxfId="46" priority="2236"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:I2">
-    <cfRule type="cellIs" dxfId="45" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P3:XFD4">
-    <cfRule type="cellIs" dxfId="44" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:AY2 L2:O4 B3:B4 D3:J4">
-    <cfRule type="cellIs" dxfId="43" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/AVAC/Ontologia_AVAC.xlsx
+++ b/Versão5/AVAC/Ontologia_AVAC.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AVAC\"/>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46152.490990509257</v>
+        <v>46214.365782638888</v>
       </c>
       <c r="C18" s="56" t="s">
         <v>207</v>

--- a/Versão5/AVAC/Ontologia_AVAC.xlsx
+++ b/Versão5/AVAC/Ontologia_AVAC.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\AVAC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB4702D-9E4E-422B-BD53-53520E857A76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B0251E7-1ACD-43CE-940A-C44F7D4CFE56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="520" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="13" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1756" uniqueCount="500">
   <si>
     <t>EquivalentTo: 
 Raiz
@@ -1481,9 +1481,6 @@
     <t>Circuito.Elétrico.de.Exaustão</t>
   </si>
   <si>
-    <t>Climatização</t>
-  </si>
-  <si>
     <t>Elétrica.de.Climatização</t>
   </si>
   <si>
@@ -1505,9 +1502,6 @@
     <t>Los calefactores utilizan una combinación de radiación natural y/o convección.</t>
   </si>
   <si>
-    <t>Arquitetura</t>
-  </si>
-  <si>
     <t>Unidade de distribuição de calor que opera com ar circulado por gravidade.</t>
   </si>
   <si>
@@ -1562,9 +1556,6 @@
     <t>"Conteiner de Dutos de Exaustão"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -1575,6 +1566,12 @@
   </si>
   <si>
     <t>Projeto_A</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Climatizações</t>
   </si>
 </sst>
 </file>
@@ -2112,71 +2109,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="80">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="73">
     <dxf>
       <font>
         <b val="0"/>
@@ -3318,14 +3251,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ED84A63-55AB-497E-9EBD-4681BB9AFAFF}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.65" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.53515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="48" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="19.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="19.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="12" t="s">
         <v>43</v>
       </c>
@@ -3336,7 +3269,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
         <v>45</v>
       </c>
@@ -3347,7 +3280,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="13" t="s">
         <v>47</v>
       </c>
@@ -3358,7 +3291,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="14" t="s">
         <v>48</v>
       </c>
@@ -3369,7 +3302,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="14" t="s">
         <v>49</v>
       </c>
@@ -3381,7 +3314,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
         <v>50</v>
       </c>
@@ -3393,7 +3326,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>51</v>
       </c>
@@ -3404,7 +3337,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
         <v>53</v>
       </c>
@@ -3415,7 +3348,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="14" t="s">
         <v>54</v>
       </c>
@@ -3426,7 +3359,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="14" t="s">
         <v>56</v>
       </c>
@@ -3437,7 +3370,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="14" t="s">
         <v>58</v>
       </c>
@@ -3448,7 +3381,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="14" t="s">
         <v>59</v>
       </c>
@@ -3459,7 +3392,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
         <v>60</v>
       </c>
@@ -3470,7 +3403,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="14" t="s">
         <v>61</v>
       </c>
@@ -3481,7 +3414,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="14" t="s">
         <v>62</v>
       </c>
@@ -3492,7 +3425,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
         <v>63</v>
       </c>
@@ -3503,7 +3436,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
         <v>64</v>
       </c>
@@ -3514,19 +3447,19 @@
         <v>206</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B18" s="16">
         <f ca="1">NOW()</f>
-        <v>46216.369106134262</v>
+        <v>46243.453108796297</v>
       </c>
       <c r="C18" s="47" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="14" t="s">
         <v>209</v>
       </c>
@@ -3537,7 +3470,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="14" t="s">
         <v>211</v>
       </c>
@@ -3549,7 +3482,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="14" t="s">
         <v>212</v>
       </c>
@@ -3561,7 +3494,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="14" t="s">
         <v>66</v>
       </c>
@@ -3572,7 +3505,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="14" t="s">
         <v>67</v>
       </c>
@@ -3583,7 +3516,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="14" t="s">
         <v>68</v>
       </c>
@@ -3594,7 +3527,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.6999999999999993" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="14" t="s">
         <v>69</v>
       </c>
@@ -3605,7 +3538,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="14" t="s">
         <v>203</v>
       </c>
@@ -3626,34 +3559,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96052D63-9637-42D9-866B-0BB924A50D8C}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA89"/>
-  <sheetFormatPr defaultColWidth="7.85546875" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="7.84375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="61" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="55" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="23.28515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="90.28515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="68.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" style="61" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69140625" style="55" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.15234375" style="55" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.3046875" style="55" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.3828125" style="55" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.15234375" style="55" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.15234375" style="55" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.3046875" style="55" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="23.3046875" style="55" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="90.3046875" style="55" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="68.84375" style="55" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="3" style="55" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="7.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="19.140625" style="55" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.28515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="8.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="16.28515625" style="55" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="21.42578125" style="55" customWidth="1"/>
-    <col min="26" max="26" width="5.5703125" style="55" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="88.42578125" style="55" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="7.85546875" style="55"/>
+    <col min="19" max="19" width="7.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="19.15234375" style="55" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.3046875" style="55" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="8.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="16.3046875" style="55" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="21.3828125" style="55" customWidth="1"/>
+    <col min="26" max="26" width="5.53515625" style="55" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="88.3828125" style="55" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="7.84375" style="55"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="63" customFormat="1" ht="41.65" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:27" s="63" customFormat="1" ht="41.7" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="59">
         <v>1</v>
       </c>
@@ -3736,12 +3669,12 @@
         <v>202</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="60">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>169</v>
@@ -3750,7 +3683,7 @@
         <v>170</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F2" s="36" t="s">
         <v>168</v>
@@ -3790,7 +3723,7 @@
         <v>218</v>
       </c>
       <c r="Q2" s="32" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="R2" s="32" t="s">
         <v>9</v>
@@ -3821,19 +3754,19 @@
         <v>9</v>
       </c>
       <c r="Z2" s="32" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="AA2" s="32" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="60">
         <v>3</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>169</v>
@@ -3842,7 +3775,7 @@
         <v>170</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F3" s="36" t="s">
         <v>219</v>
@@ -3882,7 +3815,7 @@
         <v>220</v>
       </c>
       <c r="Q3" s="32" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="R3" s="32" t="s">
         <v>9</v>
@@ -3920,12 +3853,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="60">
         <v>4</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>169</v>
@@ -3934,7 +3867,7 @@
         <v>170</v>
       </c>
       <c r="E4" s="36" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F4" s="36" t="s">
         <v>221</v>
@@ -3974,7 +3907,7 @@
         <v>222</v>
       </c>
       <c r="Q4" s="32" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="R4" s="32" t="s">
         <v>9</v>
@@ -4012,12 +3945,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="60">
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>169</v>
@@ -4026,7 +3959,7 @@
         <v>170</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F5" s="36" t="s">
         <v>223</v>
@@ -4066,7 +3999,7 @@
         <v>224</v>
       </c>
       <c r="Q5" s="32" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="R5" s="32" t="s">
         <v>9</v>
@@ -4104,12 +4037,12 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="60">
         <v>6</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>169</v>
@@ -4118,7 +4051,7 @@
         <v>170</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F6" s="36" t="s">
         <v>225</v>
@@ -4158,7 +4091,7 @@
         <v>226</v>
       </c>
       <c r="Q6" s="32" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="R6" s="32" t="s">
         <v>9</v>
@@ -4196,21 +4129,21 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="60">
         <v>7</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" s="56" t="s">
+        <v>470</v>
+      </c>
+      <c r="E7" s="56" t="s">
         <v>469</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>471</v>
-      </c>
-      <c r="E7" s="56" t="s">
-        <v>470</v>
       </c>
       <c r="F7" s="56" t="s">
         <v>466</v>
@@ -4231,15 +4164,15 @@
         <v>9</v>
       </c>
       <c r="L7" s="37" t="str">
-        <f t="shared" ref="L2:M17" si="5">CONCATENATE("", C7)</f>
-        <v>Climatização</v>
+        <f t="shared" ref="L7:M17" si="5">CONCATENATE("", C7)</f>
+        <v>Climatizações</v>
       </c>
       <c r="M7" s="37" t="str">
         <f t="shared" si="5"/>
         <v>Sistemas.Elétricos.de.Climatização</v>
       </c>
       <c r="N7" s="37" t="str">
-        <f t="shared" ref="N2:O17" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N7:N17" si="6">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
         <v>Elétrica de Climatização</v>
       </c>
       <c r="O7" s="32" t="str">
@@ -4257,7 +4190,7 @@
       </c>
       <c r="S7" s="32" t="str">
         <f t="shared" ref="S7:U22" si="8">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T7" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4284,25 +4217,25 @@
         <v>284</v>
       </c>
       <c r="AA7" s="32" t="str">
-        <f t="shared" ref="AA2:AA68" si="9">_xlfn.TRANSLATE(P7,"pt","en")</f>
+        <f t="shared" ref="AA7:AA68" si="9">_xlfn.TRANSLATE(P7,"pt","en")</f>
         <v>Electrical System for Air Conditioning</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="60">
         <v>8</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="56" t="s">
+        <v>470</v>
+      </c>
+      <c r="E8" s="56" t="s">
         <v>469</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>471</v>
-      </c>
-      <c r="E8" s="56" t="s">
-        <v>470</v>
       </c>
       <c r="F8" s="56" t="s">
         <v>467</v>
@@ -4324,7 +4257,7 @@
       </c>
       <c r="L8" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M8" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4349,7 +4282,7 @@
       </c>
       <c r="S8" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T8" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4380,21 +4313,21 @@
         <v>Electrical Heating System</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="60">
         <v>9</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="D9" s="56" t="s">
+        <v>470</v>
+      </c>
+      <c r="E9" s="56" t="s">
         <v>469</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>471</v>
-      </c>
-      <c r="E9" s="56" t="s">
-        <v>470</v>
       </c>
       <c r="F9" s="56" t="s">
         <v>468</v>
@@ -4416,7 +4349,7 @@
       </c>
       <c r="L9" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M9" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4441,7 +4374,7 @@
       </c>
       <c r="S9" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T9" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4472,21 +4405,21 @@
         <v>Electrical System for Air Exhaust</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="60">
         <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D10" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F10" s="36" t="s">
         <v>181</v>
@@ -4508,7 +4441,7 @@
       </c>
       <c r="L10" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M10" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4533,7 +4466,7 @@
       </c>
       <c r="S10" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T10" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4564,21 +4497,21 @@
         <v>Air conditioning distribution system to maintain a range of temperatures in one or more spaces.</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="60">
         <v>11</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D11" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E11" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F11" s="36" t="s">
         <v>119</v>
@@ -4600,7 +4533,7 @@
       </c>
       <c r="L11" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M11" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4625,7 +4558,7 @@
       </c>
       <c r="S11" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T11" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4656,21 +4589,21 @@
         <v>Non-potable chilled water, such as that circulated through an evaporator.</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="60">
         <v>12</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D12" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E12" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F12" s="36" t="s">
         <v>456</v>
@@ -4692,7 +4625,7 @@
       </c>
       <c r="L12" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M12" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4717,7 +4650,7 @@
       </c>
       <c r="S12" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T12" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4748,21 +4681,21 @@
         <v>Non-potable water, such as that circulated through a condemner.</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="60">
         <v>13</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D13" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E13" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F13" s="36" t="s">
         <v>185</v>
@@ -4784,7 +4717,7 @@
       </c>
       <c r="L13" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M13" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4809,7 +4742,7 @@
       </c>
       <c r="S13" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T13" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4840,21 +4773,21 @@
         <v>Compressed air system.</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="60">
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D14" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E14" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F14" s="36" t="s">
         <v>186</v>
@@ -4876,7 +4809,7 @@
       </c>
       <c r="L14" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M14" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4901,7 +4834,7 @@
       </c>
       <c r="S14" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T14" s="32" t="str">
         <f t="shared" si="8"/>
@@ -4932,21 +4865,21 @@
         <v>Exhaust air collection system to remove stale or harmful air from one or more spaces.</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="60">
         <v>15</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D15" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F15" s="36" t="s">
         <v>182</v>
@@ -4968,7 +4901,7 @@
       </c>
       <c r="L15" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M15" s="37" t="str">
         <f t="shared" si="5"/>
@@ -4993,7 +4926,7 @@
       </c>
       <c r="S15" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T15" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5024,21 +4957,21 @@
         <v>Water or steam heated from a boiler and circulated through radiators.</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="60">
         <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D16" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F16" s="36" t="s">
         <v>177</v>
@@ -5060,7 +4993,7 @@
       </c>
       <c r="L16" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M16" s="37" t="str">
         <f t="shared" si="5"/>
@@ -5085,7 +5018,7 @@
       </c>
       <c r="S16" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T16" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5116,21 +5049,21 @@
         <v>Ventilation air distribution system involved in the exchange of air to the outside.</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="60">
         <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D17" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F17" s="36" t="s">
         <v>183</v>
@@ -5152,7 +5085,7 @@
       </c>
       <c r="L17" s="37" t="str">
         <f t="shared" si="5"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M17" s="37" t="str">
         <f t="shared" si="5"/>
@@ -5177,7 +5110,7 @@
       </c>
       <c r="S17" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T17" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5208,21 +5141,21 @@
         <v>A refrigerant distribution system for the purpose of fulfilling all or part of a refrigeration cycle.</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="60">
         <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D18" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F18" s="36" t="s">
         <v>464</v>
@@ -5244,7 +5177,7 @@
       </c>
       <c r="L18" s="37" t="str">
         <f t="shared" ref="L18:M36" si="11">CONCATENATE("", C18)</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M18" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5269,7 +5202,7 @@
       </c>
       <c r="S18" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T18" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5300,21 +5233,21 @@
         <v>Distribution system that forms the intended path for the supply current.</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="60">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D19" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F19" s="36" t="s">
         <v>465</v>
@@ -5336,7 +5269,7 @@
       </c>
       <c r="L19" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M19" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5361,7 +5294,7 @@
       </c>
       <c r="S19" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T19" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5392,21 +5325,21 @@
         <v>Distribution system that forms the intended path for the return current.</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="60">
         <v>20</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D20" s="56" t="s">
+        <v>471</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>472</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>473</v>
       </c>
       <c r="F20" s="36" t="s">
         <v>184</v>
@@ -5428,7 +5361,7 @@
       </c>
       <c r="L20" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M20" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5453,7 +5386,7 @@
       </c>
       <c r="S20" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T20" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5484,15 +5417,15 @@
         <v>Vacuum distribution system.</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="60">
         <v>21</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>452</v>
@@ -5520,7 +5453,7 @@
       </c>
       <c r="L21" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M21" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5545,7 +5478,7 @@
       </c>
       <c r="S21" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T21" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5576,15 +5509,15 @@
         <v>Duct connection is a junction or transition in the flow distribution system in pipelines.</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="60">
         <v>22</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>452</v>
@@ -5612,7 +5545,7 @@
       </c>
       <c r="L22" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M22" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5637,7 +5570,7 @@
       </c>
       <c r="S22" s="32" t="str">
         <f t="shared" si="8"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T22" s="32" t="str">
         <f t="shared" si="8"/>
@@ -5668,15 +5601,15 @@
         <v>Flexible segments are a continuous nonlinear segment of the duct that can be deformed.</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="60">
         <v>23</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>452</v>
@@ -5704,7 +5637,7 @@
       </c>
       <c r="L23" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M23" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5729,7 +5662,7 @@
       </c>
       <c r="S23" s="32" t="str">
         <f t="shared" ref="S23:U38" si="13">SUBSTITUTE(C23, "_", " ")</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T23" s="32" t="str">
         <f t="shared" si="13"/>
@@ -5760,15 +5693,15 @@
         <v>Duct segments are typically used to join two sections of the duct network.</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="60">
         <v>24</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>452</v>
@@ -5796,7 +5729,7 @@
       </c>
       <c r="L24" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M24" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5821,7 +5754,7 @@
       </c>
       <c r="S24" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T24" s="32" t="str">
         <f t="shared" si="13"/>
@@ -5852,15 +5785,15 @@
         <v>Duct muffler is a device that is usually installed inside distribution system.</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="60">
         <v>25</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>452</v>
@@ -5888,7 +5821,7 @@
       </c>
       <c r="L25" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M25" s="37" t="str">
         <f t="shared" si="11"/>
@@ -5913,7 +5846,7 @@
       </c>
       <c r="S25" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T25" s="32" t="str">
         <f t="shared" si="13"/>
@@ -5944,15 +5877,15 @@
         <v>Duct insulator type.</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="60">
         <v>26</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>452</v>
@@ -5980,7 +5913,7 @@
       </c>
       <c r="L26" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M26" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6005,7 +5938,7 @@
       </c>
       <c r="S26" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T26" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6036,15 +5969,15 @@
         <v>Pipe connection is a junction or transition in the pipe flow distribution system.</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="60">
         <v>27</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>452</v>
@@ -6072,7 +6005,7 @@
       </c>
       <c r="L27" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M27" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6097,7 +6030,7 @@
       </c>
       <c r="S27" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T27" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6128,15 +6061,15 @@
         <v>Pipe segments is used to typically join two sections of a plumbing network.</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="60">
         <v>28</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>452</v>
@@ -6164,7 +6097,7 @@
       </c>
       <c r="L28" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M28" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6189,7 +6122,7 @@
       </c>
       <c r="S28" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T28" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6220,15 +6153,15 @@
         <v>Valve is used in plumbing distribution system for construction services.</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="60">
         <v>29</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>452</v>
@@ -6256,7 +6189,7 @@
       </c>
       <c r="L29" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M29" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6281,7 +6214,7 @@
       </c>
       <c r="S29" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T29" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6312,15 +6245,15 @@
         <v>Duct terminal, it can be a diffuser or a return mouth.</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A30" s="60">
         <v>30</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>452</v>
@@ -6348,7 +6281,7 @@
       </c>
       <c r="L30" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M30" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6373,7 +6306,7 @@
       </c>
       <c r="S30" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T30" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6404,15 +6337,15 @@
         <v>Junction box is a compartment where ducts are connected.</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="60">
         <v>31</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>452</v>
@@ -6440,7 +6373,7 @@
       </c>
       <c r="L31" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M31" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6465,7 +6398,7 @@
       </c>
       <c r="S31" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T31" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6496,15 +6429,15 @@
         <v>Air terminal box is usually part of HVAC duct distribution system.</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="60">
         <v>32</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>453</v>
@@ -6532,7 +6465,7 @@
       </c>
       <c r="L32" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M32" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6557,7 +6490,7 @@
       </c>
       <c r="S32" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T32" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6588,15 +6521,15 @@
         <v>A compressor is a device that compresses a fluid normally used in a refrigeration circuit.</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="60">
         <v>33</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>453</v>
@@ -6624,7 +6557,7 @@
       </c>
       <c r="L33" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M33" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6649,7 +6582,7 @@
       </c>
       <c r="S33" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T33" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6680,15 +6613,15 @@
         <v>A filter is a device used to remove particles or gaseous matter from fluids and gases.</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="60">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>453</v>
@@ -6716,7 +6649,7 @@
       </c>
       <c r="L34" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M34" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6741,7 +6674,7 @@
       </c>
       <c r="S34" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T34" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6772,15 +6705,15 @@
         <v>Unitary equipment usually combines several components into a single product, such as an air handle.</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="60">
         <v>35</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>453</v>
@@ -6808,7 +6741,7 @@
       </c>
       <c r="L35" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M35" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6833,7 +6766,7 @@
       </c>
       <c r="S35" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T35" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6864,15 +6797,15 @@
         <v>Bundle of tubes is a device consisting of tubes and bundles of tubes used for heat transfer and containment.</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="60">
         <v>36</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>453</v>
@@ -6900,7 +6833,7 @@
       </c>
       <c r="L36" s="37" t="str">
         <f t="shared" si="11"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M36" s="37" t="str">
         <f t="shared" si="11"/>
@@ -6925,7 +6858,7 @@
       </c>
       <c r="S36" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T36" s="32" t="str">
         <f t="shared" si="13"/>
@@ -6956,15 +6889,15 @@
         <v>A boiler is a closed piece of equipment, rated for pressure, in which water or other fluid.</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="60">
         <v>37</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>453</v>
@@ -6992,7 +6925,7 @@
       </c>
       <c r="L37" s="37" t="str">
         <f t="shared" ref="L37:M89" si="14">CONCATENATE("", C37)</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M37" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7017,7 +6950,7 @@
       </c>
       <c r="S37" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T37" s="32" t="str">
         <f t="shared" si="13"/>
@@ -7048,15 +6981,15 @@
         <v>Generally vertical ducts, used to exhaust gases from equipment such as boilers.</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="60">
         <v>38</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>453</v>
@@ -7084,7 +7017,7 @@
       </c>
       <c r="L38" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M38" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7109,7 +7042,7 @@
       </c>
       <c r="S38" s="32" t="str">
         <f t="shared" si="13"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T38" s="32" t="str">
         <f t="shared" si="13"/>
@@ -7140,15 +7073,15 @@
         <v>A device used to remove heat from a liquid through a refrigeration cycle.</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="60">
         <v>39</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>453</v>
@@ -7176,7 +7109,7 @@
       </c>
       <c r="L39" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M39" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7201,7 +7134,7 @@
       </c>
       <c r="S39" s="32" t="str">
         <f t="shared" ref="S39:U54" si="15">SUBSTITUTE(C39, "_", " ")</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T39" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7232,15 +7165,15 @@
         <v>A device used to dissipate heat, usually by condensing a substance.</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="60">
         <v>40</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>453</v>
@@ -7268,7 +7201,7 @@
       </c>
       <c r="L40" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M40" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7293,7 +7226,7 @@
       </c>
       <c r="S40" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T40" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7324,15 +7257,15 @@
         <v>A device in which a refrigerant fluid is vaporized that absorbs heat from the fluid.</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="60">
         <v>41</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>453</v>
@@ -7360,7 +7293,7 @@
       </c>
       <c r="L41" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M41" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7385,7 +7318,7 @@
       </c>
       <c r="S41" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T41" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7416,15 +7349,15 @@
         <v>A device that converts fuel into heat through combustion.</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A42" s="60">
         <v>42</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>453</v>
@@ -7452,7 +7385,7 @@
       </c>
       <c r="L42" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M42" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7477,7 +7410,7 @@
       </c>
       <c r="S42" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T42" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7508,15 +7441,15 @@
         <v>Air-to-air heat recovery device uses a countercurrent heat exchanger.</v>
       </c>
     </row>
-    <row r="43" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A43" s="60">
         <v>43</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>453</v>
@@ -7544,7 +7477,7 @@
       </c>
       <c r="L43" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M43" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7569,7 +7502,7 @@
       </c>
       <c r="S43" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T43" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7600,15 +7533,15 @@
         <v>A device that cools the air by saturating it with water vapor.</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A44" s="60">
         <v>44</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>453</v>
@@ -7636,7 +7569,7 @@
       </c>
       <c r="L44" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M44" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7661,7 +7594,7 @@
       </c>
       <c r="S44" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T44" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7692,15 +7625,15 @@
         <v>Coil is a device used to provide heat transfer between the unmixed media.</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A45" s="60">
         <v>45</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>453</v>
@@ -7728,7 +7661,7 @@
       </c>
       <c r="L45" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M45" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7753,7 +7686,7 @@
       </c>
       <c r="S45" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T45" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7784,15 +7717,15 @@
         <v>Cooling tower is a device that rejects heat into ambient air by circulating a fluid.</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A46" s="60">
         <v>46</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D46" s="1" t="s">
         <v>453</v>
@@ -7820,7 +7753,7 @@
       </c>
       <c r="L46" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M46" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7845,7 +7778,7 @@
       </c>
       <c r="S46" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T46" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7876,15 +7809,15 @@
         <v>Heat exchanger is a device used to provide heat transfer between media.</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A47" s="60">
         <v>47</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D47" s="1" t="s">
         <v>453</v>
@@ -7912,7 +7845,7 @@
       </c>
       <c r="L47" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M47" s="37" t="str">
         <f t="shared" si="14"/>
@@ -7937,7 +7870,7 @@
       </c>
       <c r="S47" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T47" s="32" t="str">
         <f t="shared" si="15"/>
@@ -7968,15 +7901,15 @@
         <v>Device that adds moisture to the air.</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A48" s="60">
         <v>48</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>453</v>
@@ -8004,7 +7937,7 @@
       </c>
       <c r="L48" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M48" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8029,7 +7962,7 @@
       </c>
       <c r="S48" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T48" s="32" t="str">
         <f t="shared" si="15"/>
@@ -8060,24 +7993,24 @@
         <v>A fan is a device that transmits mechanical work to a gas.</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A49" s="60">
         <v>49</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D49" s="1" t="s">
         <v>453</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F49" s="36" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="G49" s="64" t="s">
         <v>9</v>
@@ -8096,7 +8029,7 @@
       </c>
       <c r="L49" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M49" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8111,17 +8044,17 @@
         <v>Avac Aquecedor de Ambiente</v>
       </c>
       <c r="P49" s="32" t="s">
+        <v>474</v>
+      </c>
+      <c r="Q49" s="32" t="s">
         <v>475</v>
-      </c>
-      <c r="Q49" s="32" t="s">
-        <v>476</v>
       </c>
       <c r="R49" s="32" t="s">
         <v>9</v>
       </c>
       <c r="S49" s="32" t="str">
         <f t="shared" ref="S49:S51" si="17">SUBSTITUTE(C49, ".", " ")</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T49" s="32" t="str">
         <f t="shared" ref="T49:T51" si="18">SUBSTITUTE(D49, ".", " ")</f>
@@ -8132,17 +8065,17 @@
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="V49" s="32" t="s">
-        <v>477</v>
+        <v>227</v>
       </c>
       <c r="W49" s="58" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-49</v>
       </c>
       <c r="X49" s="32" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y49" s="31" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="Z49" s="32" t="s">
         <v>282</v>
@@ -8152,24 +8085,24 @@
         <v>Space heaters use a combination of natural radiation and/or convection.</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A50" s="60">
         <v>50</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D50" s="1" t="s">
         <v>453</v>
       </c>
       <c r="E50" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="F50" s="36" t="s">
         <v>482</v>
-      </c>
-      <c r="F50" s="36" t="s">
-        <v>484</v>
       </c>
       <c r="G50" s="64" t="s">
         <v>9</v>
@@ -8188,7 +8121,7 @@
       </c>
       <c r="L50" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M50" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8203,17 +8136,17 @@
         <v>Avac Aquecedor Convector</v>
       </c>
       <c r="P50" s="32" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="Q50" s="32" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="R50" s="32" t="s">
         <v>9</v>
       </c>
       <c r="S50" s="32" t="str">
         <f t="shared" si="17"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T50" s="32" t="str">
         <f t="shared" si="18"/>
@@ -8224,17 +8157,17 @@
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="V50" s="32" t="s">
-        <v>477</v>
+        <v>227</v>
       </c>
       <c r="W50" s="58" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-50</v>
       </c>
       <c r="X50" s="32" t="s">
+        <v>484</v>
+      </c>
+      <c r="Y50" s="31" t="s">
         <v>486</v>
-      </c>
-      <c r="Y50" s="31" t="s">
-        <v>488</v>
       </c>
       <c r="Z50" s="32" t="s">
         <v>282</v>
@@ -8244,24 +8177,24 @@
         <v>Heat distribution unit that operates with air circulated by gravity.</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A51" s="60">
         <v>51</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D51" s="1" t="s">
         <v>453</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F51" s="36" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G51" s="64" t="s">
         <v>9</v>
@@ -8280,7 +8213,7 @@
       </c>
       <c r="L51" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M51" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8295,17 +8228,17 @@
         <v>Avac Aquecedor Radiação</v>
       </c>
       <c r="P51" s="32" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="Q51" s="32" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="R51" s="32" t="s">
         <v>9</v>
       </c>
       <c r="S51" s="32" t="str">
         <f t="shared" si="17"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T51" s="32" t="str">
         <f t="shared" si="18"/>
@@ -8316,17 +8249,17 @@
         <v>Avac Equipamentos Unitarios</v>
       </c>
       <c r="V51" s="32" t="s">
-        <v>477</v>
+        <v>227</v>
       </c>
       <c r="W51" s="58" t="str">
         <f t="shared" si="4"/>
         <v>Key-AVAC-51</v>
       </c>
       <c r="X51" s="32" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="Y51" s="31" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="Z51" s="32" t="s">
         <v>282</v>
@@ -8336,15 +8269,15 @@
         <v>Heat distribution unit that operates with thermal radiation.</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A52" s="60">
         <v>52</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D52" s="35" t="s">
         <v>454</v>
@@ -8372,7 +8305,7 @@
       </c>
       <c r="L52" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M52" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8397,7 +8330,7 @@
       </c>
       <c r="S52" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T52" s="32" t="str">
         <f t="shared" si="15"/>
@@ -8428,15 +8361,15 @@
         <v>Damper typically participates in HVAC duct distribution system and is used to control or modulate.</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A53" s="60">
         <v>53</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D53" s="35" t="s">
         <v>454</v>
@@ -8464,7 +8397,7 @@
       </c>
       <c r="L53" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M53" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8489,7 +8422,7 @@
       </c>
       <c r="S53" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T53" s="32" t="str">
         <f t="shared" si="15"/>
@@ -8520,15 +8453,15 @@
         <v>Vibration damper is a device used to minimize the effects of vibration on a structure.</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A54" s="60">
         <v>54</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D54" s="35" t="s">
         <v>454</v>
@@ -8556,7 +8489,7 @@
       </c>
       <c r="L54" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M54" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8581,7 +8514,7 @@
       </c>
       <c r="S54" s="32" t="str">
         <f t="shared" si="15"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T54" s="32" t="str">
         <f t="shared" si="15"/>
@@ -8612,15 +8545,15 @@
         <v>Vibration isolator is a device used to minimize the transmissibility effects of vibrations.</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A55" s="60">
         <v>55</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>455</v>
@@ -8648,7 +8581,7 @@
       </c>
       <c r="L55" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M55" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8673,7 +8606,7 @@
       </c>
       <c r="S55" s="32" t="str">
         <f t="shared" ref="S55:U87" si="20">SUBSTITUTE(C55, ".", " ")</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T55" s="32" t="str">
         <f t="shared" si="20"/>
@@ -8704,15 +8637,15 @@
         <v>A sensor is a device that measures a physical quantity and converts it into a signal that can be read. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A56" s="60">
         <v>56</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>455</v>
@@ -8740,7 +8673,7 @@
       </c>
       <c r="L56" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M56" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8765,7 +8698,7 @@
       </c>
       <c r="S56" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T56" s="32" t="str">
         <f t="shared" si="20"/>
@@ -8796,15 +8729,15 @@
         <v>A device that identifies or detects carbon monoxide. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A57" s="60">
         <v>57</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>455</v>
@@ -8832,7 +8765,7 @@
       </c>
       <c r="L57" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M57" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8857,7 +8790,7 @@
       </c>
       <c r="S57" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T57" s="32" t="str">
         <f t="shared" si="20"/>
@@ -8888,15 +8821,15 @@
         <v>A device that identifies or detects carbon dioxide. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A58" s="60">
         <v>58</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D58" s="1" t="s">
         <v>455</v>
@@ -8924,7 +8857,7 @@
       </c>
       <c r="L58" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M58" s="37" t="str">
         <f t="shared" si="14"/>
@@ -8949,7 +8882,7 @@
       </c>
       <c r="S58" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T58" s="32" t="str">
         <f t="shared" si="20"/>
@@ -8980,15 +8913,15 @@
         <v>A device that detects or detects electrical conductance. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A59" s="60">
         <v>59</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D59" s="1" t="s">
         <v>455</v>
@@ -9016,7 +8949,7 @@
       </c>
       <c r="L59" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M59" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9041,7 +8974,7 @@
       </c>
       <c r="S59" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T59" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9072,15 +9005,15 @@
         <v>A device that senses or detects contact, such as to detect if a door is closed. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A60" s="60">
         <v>60</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>455</v>
@@ -9108,7 +9041,7 @@
       </c>
       <c r="L60" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M60" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9133,7 +9066,7 @@
       </c>
       <c r="S60" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T60" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9164,15 +9097,15 @@
         <v>A device that senses or detects the seismic wave and measures the seismic intensity in the event of an earthquake. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A61" s="60">
         <v>61</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D61" s="1" t="s">
         <v>455</v>
@@ -9200,7 +9133,7 @@
       </c>
       <c r="L61" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M61" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9225,7 +9158,7 @@
       </c>
       <c r="S61" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T61" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9256,15 +9189,15 @@
         <v>Combined detector device (multi-criteria). It can detect the presence of heat, fire and smoke. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A62" s="60">
         <v>62</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D62" s="1" t="s">
         <v>455</v>
@@ -9292,7 +9225,7 @@
       </c>
       <c r="L62" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M62" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9317,7 +9250,7 @@
       </c>
       <c r="S62" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T62" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9348,15 +9281,15 @@
         <v>A device that identifies or detects flow in a fluid. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A63" s="60">
         <v>63</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C63" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D63" s="1" t="s">
         <v>455</v>
@@ -9384,7 +9317,7 @@
       </c>
       <c r="L63" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M63" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9409,7 +9342,7 @@
       </c>
       <c r="S63" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T63" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9440,15 +9373,15 @@
         <v>A device that senses or detects foreign objects that interfere with the power grid. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A64" s="60">
         <v>64</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C64" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>455</v>
@@ -9476,7 +9409,7 @@
       </c>
       <c r="L64" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M64" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9501,7 +9434,7 @@
       </c>
       <c r="S64" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T64" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9532,15 +9465,15 @@
         <v>Device that identifies or detects freezing in a window. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A65" s="60">
         <v>65</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D65" s="1" t="s">
         <v>455</v>
@@ -9568,7 +9501,7 @@
       </c>
       <c r="L65" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M65" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9593,7 +9526,7 @@
       </c>
       <c r="S65" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T65" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9624,15 +9557,15 @@
         <v>A device that detects or detects gas concentration (except CO2). Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A66" s="60">
         <v>66</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D66" s="1" t="s">
         <v>455</v>
@@ -9660,7 +9593,7 @@
       </c>
       <c r="L66" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M66" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9685,7 +9618,7 @@
       </c>
       <c r="S66" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T66" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9716,15 +9649,15 @@
         <v>A device that identifies or detects heat. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="67" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A67" s="60">
         <v>67</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C67" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D67" s="1" t="s">
         <v>455</v>
@@ -9752,7 +9685,7 @@
       </c>
       <c r="L67" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M67" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9777,7 +9710,7 @@
       </c>
       <c r="S67" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T67" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9808,15 +9741,15 @@
         <v>Device that identifies or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A68" s="60">
         <v>68</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>455</v>
@@ -9844,7 +9777,7 @@
       </c>
       <c r="L68" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M68" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9869,7 +9802,7 @@
       </c>
       <c r="S68" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T68" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9900,15 +9833,15 @@
         <v>A device that reads a label, such as to gain access to a door or elevator. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A69" s="60">
         <v>69</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C69" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D69" s="1" t="s">
         <v>455</v>
@@ -9936,7 +9869,7 @@
       </c>
       <c r="L69" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M69" s="37" t="str">
         <f t="shared" si="14"/>
@@ -9961,7 +9894,7 @@
       </c>
       <c r="S69" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T69" s="32" t="str">
         <f t="shared" si="20"/>
@@ -9992,15 +9925,15 @@
         <v>A device that senses or detects the concentration of ion, such as to measure the hardness of water. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A70" s="60">
         <v>70</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D70" s="1" t="s">
         <v>455</v>
@@ -10028,7 +9961,7 @@
       </c>
       <c r="L70" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M70" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10053,7 +9986,7 @@
       </c>
       <c r="S70" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T70" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10084,15 +10017,15 @@
         <v>A device that senses or detects the fill level, such as for a tank. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A71" s="60">
         <v>71</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D71" s="1" t="s">
         <v>455</v>
@@ -10120,7 +10053,7 @@
       </c>
       <c r="L71" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M71" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10145,7 +10078,7 @@
       </c>
       <c r="S71" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T71" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10176,15 +10109,15 @@
         <v>A device that identifies or detects light. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A72" s="60">
         <v>72</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D72" s="1" t="s">
         <v>455</v>
@@ -10212,7 +10145,7 @@
       </c>
       <c r="L72" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M72" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10237,7 +10170,7 @@
       </c>
       <c r="S72" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T72" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10268,15 +10201,15 @@
         <v>Device that senses or detects moisture. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A73" s="60">
         <v>73</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C73" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D73" s="1" t="s">
         <v>455</v>
@@ -10304,7 +10237,7 @@
       </c>
       <c r="L73" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M73" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10329,7 +10262,7 @@
       </c>
       <c r="S73" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T73" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10360,15 +10293,15 @@
         <v>A device that identifies or detects motion. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A74" s="60">
         <v>74</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>455</v>
@@ -10396,7 +10329,7 @@
       </c>
       <c r="L74" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M74" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10421,7 +10354,7 @@
       </c>
       <c r="S74" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T74" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10452,15 +10385,15 @@
         <v>Device that detects or detects any obstacles. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A75" s="60">
         <v>75</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D75" s="1" t="s">
         <v>455</v>
@@ -10488,7 +10421,7 @@
       </c>
       <c r="L75" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M75" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10513,7 +10446,7 @@
       </c>
       <c r="S75" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T75" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10544,15 +10477,15 @@
         <v>Device that identifies or detects acidity. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A76" s="60">
         <v>76</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D76" s="1" t="s">
         <v>455</v>
@@ -10580,7 +10513,7 @@
       </c>
       <c r="L76" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M76" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10605,7 +10538,7 @@
       </c>
       <c r="S76" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T76" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10636,15 +10569,15 @@
         <v>Device that senses or senses pressure. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A77" s="60">
         <v>77</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C77" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D77" s="1" t="s">
         <v>455</v>
@@ -10672,7 +10605,7 @@
       </c>
       <c r="L77" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M77" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10697,7 +10630,7 @@
       </c>
       <c r="S77" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T77" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10728,15 +10661,15 @@
         <v>A device that senses or detects radiation. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="78" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A78" s="60">
         <v>78</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C78" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>455</v>
@@ -10764,7 +10697,7 @@
       </c>
       <c r="L78" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M78" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10789,7 +10722,7 @@
       </c>
       <c r="S78" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T78" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10820,15 +10753,15 @@
         <v>A device that senses or detects atomic decay. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="79" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A79" s="60">
         <v>79</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C79" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D79" s="1" t="s">
         <v>455</v>
@@ -10856,7 +10789,7 @@
       </c>
       <c r="L79" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M79" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10881,7 +10814,7 @@
       </c>
       <c r="S79" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T79" s="32" t="str">
         <f t="shared" si="20"/>
@@ -10912,15 +10845,15 @@
         <v>A device that perceives or collects information related to rainfall. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A80" s="60">
         <v>80</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C80" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D80" s="1" t="s">
         <v>455</v>
@@ -10948,7 +10881,7 @@
       </c>
       <c r="L80" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M80" s="37" t="str">
         <f t="shared" si="14"/>
@@ -10973,7 +10906,7 @@
       </c>
       <c r="S80" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T80" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11004,15 +10937,15 @@
         <v>Device that identifies or detects smoke. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A81" s="60">
         <v>81</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C81" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>455</v>
@@ -11040,7 +10973,7 @@
       </c>
       <c r="L81" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M81" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11065,7 +10998,7 @@
       </c>
       <c r="S81" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T81" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11096,15 +11029,15 @@
         <v>A device that perceives or measures the depth of accumulated snow. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A82" s="60">
         <v>82</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C82" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>455</v>
@@ -11132,7 +11065,7 @@
       </c>
       <c r="L82" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M82" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11157,7 +11090,7 @@
       </c>
       <c r="S82" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T82" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11188,15 +11121,15 @@
         <v>A device that identifies or detects sound. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A83" s="60">
         <v>83</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C83" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>455</v>
@@ -11224,7 +11157,7 @@
       </c>
       <c r="L83" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M83" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11249,7 +11182,7 @@
       </c>
       <c r="S83" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T83" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11280,15 +11213,15 @@
         <v>Device that identifies or detects temperature. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A84" s="60">
         <v>84</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D84" s="1" t="s">
         <v>455</v>
@@ -11316,7 +11249,7 @@
       </c>
       <c r="L84" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M84" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11341,7 +11274,7 @@
       </c>
       <c r="S84" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T84" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11372,15 +11305,15 @@
         <v>A device that is placed at the rear end of the last car of a train acting on a fixed equipment. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A85" s="60">
         <v>85</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C85" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D85" s="1" t="s">
         <v>455</v>
@@ -11408,7 +11341,7 @@
       </c>
       <c r="L85" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M85" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11433,7 +11366,7 @@
       </c>
       <c r="S85" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T85" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11464,15 +11397,15 @@
         <v>A device that detects or detects the position of a blade of an AMV. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A86" s="60">
         <v>86</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>455</v>
@@ -11500,7 +11433,7 @@
       </c>
       <c r="L86" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M86" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11525,7 +11458,7 @@
       </c>
       <c r="S86" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T86" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11556,15 +11489,15 @@
         <v>A device that senses or detects the passage of a wheel. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A87" s="60">
         <v>87</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C87" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D87" s="1" t="s">
         <v>455</v>
@@ -11592,7 +11525,7 @@
       </c>
       <c r="L87" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M87" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11617,7 +11550,7 @@
       </c>
       <c r="S87" s="32" t="str">
         <f t="shared" si="20"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T87" s="32" t="str">
         <f t="shared" si="20"/>
@@ -11648,18 +11581,18 @@
         <v>A device that perceives or senses the speed and direction of airflow. Verify (MQTT) message queuing telemetry transport.</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A88" s="60">
         <v>88</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>413</v>
@@ -11684,7 +11617,7 @@
       </c>
       <c r="L88" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M88" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11709,7 +11642,7 @@
       </c>
       <c r="S88" s="32" t="str">
         <f t="shared" ref="S88:U89" si="24">SUBSTITUTE(C88, "_", " ")</f>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T88" s="32" t="str">
         <f t="shared" si="24"/>
@@ -11740,18 +11673,18 @@
         <v>HVAC duct accessories.</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:27" ht="6.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A89" s="60">
         <v>89</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>413</v>
@@ -11776,7 +11709,7 @@
       </c>
       <c r="L89" s="37" t="str">
         <f t="shared" si="14"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="M89" s="37" t="str">
         <f t="shared" si="14"/>
@@ -11801,7 +11734,7 @@
       </c>
       <c r="S89" s="32" t="str">
         <f t="shared" si="24"/>
-        <v>Climatização</v>
+        <v>Climatizações</v>
       </c>
       <c r="T89" s="32" t="str">
         <f t="shared" si="24"/>
@@ -11833,140 +11766,128 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A89">
-    <cfRule type="cellIs" dxfId="79" priority="34" operator="equal">
+  <conditionalFormatting sqref="A2:A89">
+    <cfRule type="cellIs" dxfId="72" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D55:F87 L55:Q87 S55:U87 X55:Y87 E88:E89">
-    <cfRule type="cellIs" dxfId="78" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="71" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="F1 F7:F1048576">
+    <cfRule type="duplicateValues" dxfId="70" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="9"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="77" priority="2321"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="2321"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1 F7:F1048576">
-    <cfRule type="duplicateValues" dxfId="76" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="8"/>
+  <conditionalFormatting sqref="F3:F6">
+    <cfRule type="duplicateValues" dxfId="67" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7:F9">
-    <cfRule type="duplicateValues" dxfId="70" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="35"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F20">
-    <cfRule type="duplicateValues" dxfId="68" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="66"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10:F48 F52:F89">
-    <cfRule type="duplicateValues" dxfId="67" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="36"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F22 F88:F89">
-    <cfRule type="duplicateValues" dxfId="66" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21:F22">
-    <cfRule type="duplicateValues" dxfId="65" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F23:F29">
-    <cfRule type="duplicateValues" dxfId="64" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="70"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F30:F31">
-    <cfRule type="duplicateValues" dxfId="60" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F33">
-    <cfRule type="duplicateValues" dxfId="58" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="52"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F32:F48">
-    <cfRule type="duplicateValues" dxfId="54" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="50"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F34:F48">
-    <cfRule type="duplicateValues" dxfId="53" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="51"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F49:F51 L49:Q51 S49:V51 X49:Y51 AA49:XFD51">
-    <cfRule type="cellIs" dxfId="51" priority="10" operator="equal">
+  <conditionalFormatting sqref="F49:F51 L49:Q51 S49:U51 X49:Y51 AA49:XFD51">
+    <cfRule type="cellIs" dxfId="44" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F49:F51">
-    <cfRule type="duplicateValues" dxfId="50" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="14"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F52:F54">
-    <cfRule type="duplicateValues" dxfId="40" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:F87">
-    <cfRule type="duplicateValues" dxfId="33" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="37"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88:F89 F10:F48 F52:F54">
-    <cfRule type="duplicateValues" dxfId="27" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="45"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88:F89 F21:F31">
-    <cfRule type="duplicateValues" dxfId="26" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="57"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F88:F89">
-    <cfRule type="duplicateValues" dxfId="25" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F90:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="24" priority="2323"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F90:F1048576 F1">
-    <cfRule type="duplicateValues" dxfId="23" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="2323"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F90:F1048576">
-    <cfRule type="duplicateValues" dxfId="22" priority="2330"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2326"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="2328"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="2329"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="2330"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2326"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="2328"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="2329"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1">
-    <cfRule type="cellIs" dxfId="18" priority="95" operator="equal">
+  <conditionalFormatting sqref="AA1:AA6">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA10:AA48 AA52:AA89">
-    <cfRule type="cellIs" dxfId="17" priority="46" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="46" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -11978,15 +11899,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U3"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="8.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="11" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="9" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="9"/>
+    <col min="1" max="1" width="1.3046875" style="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="9" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="4" customFormat="1" ht="16.5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="4" customFormat="1" ht="15.45" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -12051,7 +11972,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" s="4" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6">
         <v>2</v>
       </c>
@@ -12116,7 +12037,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:21" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="6">
         <v>3</v>
       </c>
@@ -12183,7 +12104,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12199,15 +12120,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5FE5EC8-1387-4A67-960C-C64BD1326958}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:G2"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" style="26" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="26" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="10.85546875" style="26" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.84375" style="26" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.3046875" style="26" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="10.84375" style="26" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="28.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="28.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="33">
         <v>0</v>
       </c>
@@ -12230,7 +12151,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="34">
         <v>2</v>
       </c>
@@ -12256,22 +12177,22 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="15" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:G1 C2:G2">
-    <cfRule type="containsText" dxfId="14" priority="2" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="7" priority="2" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="13" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B3:G1048576">
-    <cfRule type="containsText" dxfId="10" priority="8" operator="containsText" text="null">
+    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="null">
       <formula>NOT(ISERROR(SEARCH("null",B3)))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -12283,34 +12204,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38CB0525-EDFB-44CB-9009-6752AEDD7340}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:W4"/>
-  <sheetFormatPr defaultColWidth="64.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="64.3046875" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.53515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.3046875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="3.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.3828125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.84375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="3.84375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="23" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.85546875" style="55" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="56.140625" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="81.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="5.53515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.84375" style="55" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.84375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.3046875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.3828125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="56.15234375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.69140625" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="81.3046875" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="7.3046875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="10.15234375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" ht="17.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18" t="s">
         <v>10</v>
       </c>
@@ -12381,12 +12302,12 @@
         <v>78</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="7.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="21">
         <v>2</v>
       </c>
       <c r="B2" s="54" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="C2" s="51" t="s">
         <v>168</v>
@@ -12422,7 +12343,7 @@
         <v>166</v>
       </c>
       <c r="N2" s="41" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="O2" s="24" t="s">
         <v>167</v>
@@ -12452,7 +12373,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:23" s="50" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" s="50" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="21">
         <v>3</v>
       </c>
@@ -12466,7 +12387,7 @@
         <v>171</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F3" s="49" t="s">
         <v>9</v>
@@ -12484,7 +12405,7 @@
         <v>74</v>
       </c>
       <c r="K3" s="23" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="L3" s="42" t="s">
         <v>9</v>
@@ -12517,13 +12438,13 @@
         <v>217</v>
       </c>
       <c r="V3" s="42" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="W3" s="25" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
     </row>
-    <row r="4" spans="1:23" s="50" customFormat="1" ht="7.15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" s="50" customFormat="1" ht="7.2" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="21">
         <v>4</v>
       </c>
@@ -12537,7 +12458,7 @@
         <v>171</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F4" s="49" t="s">
         <v>9</v>
@@ -12555,7 +12476,7 @@
         <v>74</v>
       </c>
       <c r="K4" s="23" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="L4" s="42" t="s">
         <v>9</v>
@@ -12588,24 +12509,24 @@
         <v>217</v>
       </c>
       <c r="V4" s="42" t="s">
+        <v>489</v>
+      </c>
+      <c r="W4" s="25" t="s">
         <v>491</v>
-      </c>
-      <c r="W4" s="25" t="s">
-        <v>493</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B3:B4">
-    <cfRule type="duplicateValues" dxfId="9" priority="2236"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="2236"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:I2 L3:Q4 V3:XFD4">
-    <cfRule type="cellIs" dxfId="8" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V2:W2 R2:U4 B3:B4 D3:J4">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
